--- a/model/Outputs/11. Interest rate/20/Output Files/0.3/Output_6_36.xlsx
+++ b/model/Outputs/11. Interest rate/20/Output Files/0.3/Output_6_36.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1859182.113950345</v>
+        <v>1851285.663886918</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7154817.030747599</v>
+        <v>7154817.030747601</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7154817.030747599</v>
+        <v>7154817.030747601</v>
       </c>
     </row>
     <row r="9">
@@ -702,10 +702,10 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>28.70619138541469</v>
       </c>
       <c r="S2" t="n">
-        <v>123.5543591877376</v>
+        <v>94.84816780232291</v>
       </c>
       <c r="T2" t="n">
         <v>186.6755817285639</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -748,7 +748,7 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>119.5822865038921</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -781,10 +781,10 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R3" t="n">
-        <v>385</v>
+        <v>147.2737972923793</v>
       </c>
       <c r="S3" t="n">
-        <v>296.3577706585854</v>
+        <v>66.5639999646113</v>
       </c>
       <c r="T3" t="n">
         <v>5.357765217513816</v>
@@ -842,7 +842,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>23.54762815777917</v>
+        <v>21.95645751172319</v>
       </c>
       <c r="M4" t="n">
         <v>120.6316114025499</v>
@@ -854,7 +854,7 @@
         <v>240.445564079015</v>
       </c>
       <c r="P4" t="n">
-        <v>285.8567266822216</v>
+        <v>287.4478973282775</v>
       </c>
       <c r="Q4" t="n">
         <v>325.839266425598</v>
@@ -970,7 +970,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>299.6463592929433</v>
+        <v>2.338019733153759</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -979,10 +979,10 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -1039,7 +1039,7 @@
         <v>19.86273944538755</v>
       </c>
       <c r="Y6" t="n">
-        <v>385</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1149,7 +1149,7 @@
         <v>8.009658703527407</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>28.70619138541446</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1179,7 +1179,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>123.5543591877376</v>
+        <v>94.84816780232291</v>
       </c>
       <c r="T8" t="n">
         <v>186.6755817285639</v>
@@ -1252,28 +1252,28 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>160.8572994597625</v>
+        <v>385</v>
       </c>
       <c r="S9" t="n">
-        <v>385</v>
+        <v>66.5639999646113</v>
       </c>
       <c r="T9" t="n">
         <v>5.357765217513816</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2103597601867477</v>
+        <v>385</v>
       </c>
       <c r="V9" t="n">
         <v>14.51066719152016</v>
       </c>
       <c r="W9" t="n">
-        <v>385</v>
+        <v>32.37314290982852</v>
       </c>
       <c r="X9" t="n">
-        <v>19.86273944538755</v>
+        <v>255.0725208813765</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -1559,7 +1559,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>340.7767994885277</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1571,10 +1571,10 @@
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>203.4033197856722</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>137.3734797028554</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -1620,7 +1620,7 @@
         <v>178.7573722870162</v>
       </c>
       <c r="H14" t="n">
-        <v>183.0096587035274</v>
+        <v>188.5028512606473</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1650,7 +1650,7 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>31.37179138541422</v>
+        <v>25.87859882829446</v>
       </c>
       <c r="S14" t="n">
         <v>269.8481678023229</v>
@@ -1760,19 +1760,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>62.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>60.53621805555548</v>
       </c>
       <c r="E16" t="n">
         <v>55.98090483695654</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3996163320670918</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -1787,7 +1787,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>63.52077380114304</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>162.1117126335823</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -1811,7 +1811,7 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>137.3734797028554</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -1823,13 +1823,13 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.372809838709685</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>22.44364543010755</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>62.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1842,7 +1842,7 @@
         <v>256.9993129555745</v>
       </c>
       <c r="C17" t="n">
-        <v>224.4745782429939</v>
+        <v>229.9677708001137</v>
       </c>
       <c r="D17" t="n">
         <v>185.3391557398498</v>
@@ -1857,7 +1857,7 @@
         <v>178.7573722870162</v>
       </c>
       <c r="H17" t="n">
-        <v>188.5028512606473</v>
+        <v>183.0096587035274</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>62.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>47.72524664804467</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>31.09891995108653</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -2036,7 +2036,7 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>340.7767994885277</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
@@ -2048,7 +2048,7 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>137.3734797028554</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2066,7 +2066,7 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>62.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2076,7 +2076,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>256.9993129555745</v>
+        <v>262.4925055126944</v>
       </c>
       <c r="C20" t="n">
         <v>224.4745782429939</v>
@@ -2097,7 +2097,7 @@
         <v>183.0096587035274</v>
       </c>
       <c r="I20" t="n">
-        <v>5.493192557119869</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>342.1496093272373</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
@@ -2282,7 +2282,7 @@
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>340.7767994885277</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -2297,7 +2297,7 @@
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.372809838709685</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2331,7 +2331,7 @@
         <v>178.7573722870162</v>
       </c>
       <c r="H23" t="n">
-        <v>188.5028512606473</v>
+        <v>183.0096587035274</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2382,7 +2382,7 @@
         <v>367.2818334606677</v>
       </c>
       <c r="Y23" t="n">
-        <v>286.3174326828064</v>
+        <v>291.8106252399262</v>
       </c>
     </row>
     <row r="24">
@@ -2489,7 +2489,7 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>3.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -2501,7 +2501,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>198.5476281577792</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -2519,7 +2519,7 @@
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>340.7767994885277</v>
+        <v>147.3731072710768</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.372809838709685</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
         <v>0</v>
@@ -2790,7 +2790,7 @@
         <v>256.9993129555745</v>
       </c>
       <c r="C29" t="n">
-        <v>224.4745782429939</v>
+        <v>229.9677708001137</v>
       </c>
       <c r="D29" t="n">
         <v>185.3391557398498</v>
@@ -2808,7 +2808,7 @@
         <v>183.0096587035274</v>
       </c>
       <c r="I29" t="n">
-        <v>5.493192557119869</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2957,7 +2957,7 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>46.51799792468744</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -2978,7 +2978,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>295.6316114025499</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -2993,10 +2993,10 @@
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>203.4033197856722</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>137.3734797028554</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -3008,7 +3008,7 @@
         <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.372809838709685</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
         <v>0</v>
@@ -3072,7 +3072,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>25.87859882829446</v>
+        <v>31.37179138541422</v>
       </c>
       <c r="S32" t="n">
         <v>269.8481678023229</v>
@@ -3084,7 +3084,7 @@
         <v>424.2212965486107</v>
       </c>
       <c r="V32" t="n">
-        <v>410.344216723944</v>
+        <v>404.8510241668239</v>
       </c>
       <c r="W32" t="n">
         <v>413.3734759809475</v>
@@ -3221,10 +3221,10 @@
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>319.7059638971298</v>
       </c>
       <c r="P34" t="n">
-        <v>203.4033197856722</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -3233,7 +3233,7 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>137.3734797028554</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -3245,10 +3245,10 @@
         <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.372809838709685</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>22.44364543010755</v>
       </c>
       <c r="Y34" t="n">
         <v>0</v>
@@ -3282,7 +3282,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I35" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>3.965391385414537</v>
       </c>
       <c r="S35" t="n">
         <v>144.8481678023229</v>
@@ -3358,10 +3358,10 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>195.551376634094</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I36" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3406,7 +3406,7 @@
         <v>82.37314290982852</v>
       </c>
       <c r="X36" t="n">
-        <v>69.86273944538755</v>
+        <v>150.372414784409</v>
       </c>
       <c r="Y36" t="n">
         <v>49.39139276613435</v>
@@ -3516,7 +3516,7 @@
         <v>53.75737228701621</v>
       </c>
       <c r="H38" t="n">
-        <v>61.97505008894191</v>
+        <v>58.00965870352741</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -3546,7 +3546,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>3.965391385414537</v>
       </c>
       <c r="S38" t="n">
         <v>144.8481678023229</v>
@@ -3595,7 +3595,7 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>62.67776252544248</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -3631,7 +3631,7 @@
         <v>116.5639999646113</v>
       </c>
       <c r="T39" t="n">
-        <v>55.35776521751382</v>
+        <v>118.0355277429563</v>
       </c>
       <c r="U39" t="n">
         <v>50.21035976018675</v>
@@ -3640,13 +3640,13 @@
         <v>64.51066719152016</v>
       </c>
       <c r="W39" t="n">
-        <v>82.37314290982852</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X39" t="n">
         <v>69.86273944538755</v>
       </c>
       <c r="Y39" t="n">
-        <v>399.3913927661343</v>
+        <v>49.39139276613435</v>
       </c>
     </row>
     <row r="40">
@@ -3756,7 +3756,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I41" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3783,7 +3783,7 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>3.965391385414537</v>
       </c>
       <c r="S41" t="n">
         <v>144.8481678023229</v>
@@ -3820,7 +3820,7 @@
         <v>11.09991244551929</v>
       </c>
       <c r="D42" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
@@ -3862,7 +3862,7 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>262.0138729201192</v>
+        <v>197.2737972923793</v>
       </c>
       <c r="S42" t="n">
         <v>116.5639999646113</v>
@@ -3877,10 +3877,10 @@
         <v>64.51066719152016</v>
       </c>
       <c r="W42" t="n">
-        <v>82.37314290982852</v>
+        <v>145.050905435271</v>
       </c>
       <c r="X42" t="n">
-        <v>69.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y42" t="n">
         <v>49.39139276613435</v>
@@ -3990,7 +3990,7 @@
         <v>53.75737228701621</v>
       </c>
       <c r="H44" t="n">
-        <v>58.00965870352741</v>
+        <v>61.97505008894191</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -4026,7 +4026,7 @@
         <v>144.8481678023229</v>
       </c>
       <c r="T44" t="n">
-        <v>240.6409731139784</v>
+        <v>236.6755817285639</v>
       </c>
       <c r="U44" t="n">
         <v>299.2212965486107</v>
@@ -4054,7 +4054,7 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C45" t="n">
-        <v>73.77767497096173</v>
+        <v>11.09991244551929</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
@@ -4099,10 +4099,10 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>547.2737972923793</v>
+        <v>197.2737972923793</v>
       </c>
       <c r="S45" t="n">
-        <v>116.5639999646113</v>
+        <v>179.2417624900538</v>
       </c>
       <c r="T45" t="n">
         <v>55.35776521751382</v>
@@ -4111,7 +4111,7 @@
         <v>50.21035976018675</v>
       </c>
       <c r="V45" t="n">
-        <v>64.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W45" t="n">
         <v>82.37314290982852</v>
@@ -4321,22 +4321,22 @@
         <v>30.8</v>
       </c>
       <c r="J2" t="n">
-        <v>30.8</v>
+        <v>396.55</v>
       </c>
       <c r="K2" t="n">
-        <v>30.8</v>
+        <v>396.55</v>
       </c>
       <c r="L2" t="n">
-        <v>30.8</v>
+        <v>396.55</v>
       </c>
       <c r="M2" t="n">
-        <v>411.95</v>
+        <v>777.6999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>793.0999999999999</v>
+        <v>1158.85</v>
       </c>
       <c r="O2" t="n">
-        <v>1174.25</v>
+        <v>1540</v>
       </c>
       <c r="P2" t="n">
         <v>1540</v>
@@ -4345,7 +4345,7 @@
         <v>1540</v>
       </c>
       <c r="R2" t="n">
-        <v>1540</v>
+        <v>1511.00384708544</v>
       </c>
       <c r="S2" t="n">
         <v>1415.197616982083</v>
@@ -4376,19 +4376,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>250.1195817084329</v>
+        <v>722.3619790837812</v>
       </c>
       <c r="C3" t="n">
-        <v>250.1195817084329</v>
+        <v>722.3619790837812</v>
       </c>
       <c r="D3" t="n">
-        <v>250.1195817084329</v>
+        <v>370.9097700962027</v>
       </c>
       <c r="E3" t="n">
-        <v>250.1195817084329</v>
+        <v>370.9097700962027</v>
       </c>
       <c r="F3" t="n">
-        <v>250.1195817084329</v>
+        <v>370.9097700962027</v>
       </c>
       <c r="G3" t="n">
         <v>250.1195817084329</v>
@@ -4424,28 +4424,28 @@
         <v>1011.404879873102</v>
       </c>
       <c r="R3" t="n">
-        <v>622.5159909842129</v>
+        <v>862.6434684666581</v>
       </c>
       <c r="S3" t="n">
-        <v>323.1647074906923</v>
+        <v>795.4071048660406</v>
       </c>
       <c r="T3" t="n">
-        <v>317.7528234325975</v>
+        <v>789.9952208079459</v>
       </c>
       <c r="U3" t="n">
-        <v>317.5403388263483</v>
+        <v>789.7827362016966</v>
       </c>
       <c r="V3" t="n">
-        <v>302.8830992389542</v>
+        <v>775.1254966143025</v>
       </c>
       <c r="W3" t="n">
-        <v>270.182954885592</v>
+        <v>742.4253522609404</v>
       </c>
       <c r="X3" t="n">
-        <v>250.1195817084329</v>
+        <v>722.3619790837812</v>
       </c>
       <c r="Y3" t="n">
-        <v>250.1195817084329</v>
+        <v>722.3619790837812</v>
       </c>
     </row>
     <row r="4">
@@ -4455,28 +4455,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>637.5231570163306</v>
+        <v>530.0705151524171</v>
       </c>
       <c r="C4" t="n">
-        <v>637.5231570163306</v>
+        <v>530.0705151524171</v>
       </c>
       <c r="D4" t="n">
-        <v>750.8423011413307</v>
+        <v>643.3896592774172</v>
       </c>
       <c r="E4" t="n">
-        <v>868.6712053527438</v>
+        <v>761.2185634888302</v>
       </c>
       <c r="F4" t="n">
-        <v>868.6712053527438</v>
+        <v>885.5795360807657</v>
       </c>
       <c r="G4" t="n">
-        <v>868.6712053527438</v>
+        <v>1038.986101967651</v>
       </c>
       <c r="H4" t="n">
-        <v>868.6712053527438</v>
+        <v>1208.502687127049</v>
       </c>
       <c r="I4" t="n">
-        <v>1068.55182541068</v>
+        <v>1429.635566063132</v>
       </c>
       <c r="J4" t="n">
         <v>1429.635566063132</v>
@@ -4485,16 +4485,16 @@
         <v>1540</v>
       </c>
       <c r="L4" t="n">
-        <v>1516.214517012344</v>
+        <v>1517.821760089168</v>
       </c>
       <c r="M4" t="n">
-        <v>1394.364404484516</v>
+        <v>1395.97164756134</v>
       </c>
       <c r="N4" t="n">
-        <v>1221.450187038369</v>
+        <v>1223.057430115194</v>
       </c>
       <c r="O4" t="n">
-        <v>978.5758798878493</v>
+        <v>980.1831229646734</v>
       </c>
       <c r="P4" t="n">
         <v>689.8317115219688</v>
@@ -4512,19 +4512,19 @@
         <v>68.05025509417312</v>
       </c>
       <c r="U4" t="n">
-        <v>314.6014477324597</v>
+        <v>68.05025509417312</v>
       </c>
       <c r="V4" t="n">
-        <v>314.6014477324597</v>
+        <v>266.8716479801191</v>
       </c>
       <c r="W4" t="n">
-        <v>486.4923659921371</v>
+        <v>266.8716479801191</v>
       </c>
       <c r="X4" t="n">
-        <v>637.5231570163306</v>
+        <v>417.9024390043126</v>
       </c>
       <c r="Y4" t="n">
-        <v>637.5231570163306</v>
+        <v>529.3117396833449</v>
       </c>
     </row>
     <row r="5">
@@ -4558,19 +4558,19 @@
         <v>30.8</v>
       </c>
       <c r="J5" t="n">
-        <v>411.95</v>
+        <v>30.8</v>
       </c>
       <c r="K5" t="n">
-        <v>411.95</v>
+        <v>411.9499999999999</v>
       </c>
       <c r="L5" t="n">
         <v>777.6999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>777.6999999999999</v>
+        <v>1158.85</v>
       </c>
       <c r="N5" t="n">
-        <v>1158.85</v>
+        <v>1540</v>
       </c>
       <c r="O5" t="n">
         <v>1540</v>
@@ -4613,16 +4613,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30.8</v>
+        <v>720.0003429896865</v>
       </c>
       <c r="C6" t="n">
-        <v>30.8</v>
+        <v>720.0003429896865</v>
       </c>
       <c r="D6" t="n">
-        <v>30.8</v>
+        <v>720.0003429896865</v>
       </c>
       <c r="E6" t="n">
-        <v>30.8</v>
+        <v>373.8669114524009</v>
       </c>
       <c r="F6" t="n">
         <v>30.8</v>
@@ -4682,7 +4682,7 @@
         <v>722.3619790837812</v>
       </c>
       <c r="Y6" t="n">
-        <v>333.4730901948923</v>
+        <v>722.3619790837812</v>
       </c>
     </row>
     <row r="7">
@@ -4692,31 +4692,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>576.8883476291953</v>
+        <v>616.2708981381843</v>
       </c>
       <c r="C7" t="n">
-        <v>702.8903534476311</v>
+        <v>616.2708981381843</v>
       </c>
       <c r="D7" t="n">
-        <v>816.2094975726312</v>
+        <v>729.5900422631844</v>
       </c>
       <c r="E7" t="n">
-        <v>934.0384017840443</v>
+        <v>847.4189464745974</v>
       </c>
       <c r="F7" t="n">
-        <v>1058.39937437598</v>
+        <v>847.4189464745974</v>
       </c>
       <c r="G7" t="n">
-        <v>1211.805940262865</v>
+        <v>847.4189464745974</v>
       </c>
       <c r="H7" t="n">
-        <v>1381.322525422263</v>
+        <v>847.4189464745974</v>
       </c>
       <c r="I7" t="n">
-        <v>1540</v>
+        <v>1068.55182541068</v>
       </c>
       <c r="J7" t="n">
-        <v>1540</v>
+        <v>1429.635566063132</v>
       </c>
       <c r="K7" t="n">
         <v>1540</v>
@@ -4743,25 +4743,25 @@
         <v>30.8</v>
       </c>
       <c r="S7" t="n">
-        <v>30.8</v>
+        <v>68.05025509417312</v>
       </c>
       <c r="T7" t="n">
-        <v>30.8</v>
+        <v>68.05025509417312</v>
       </c>
       <c r="U7" t="n">
-        <v>30.8</v>
+        <v>68.05025509417312</v>
       </c>
       <c r="V7" t="n">
-        <v>30.8</v>
+        <v>266.8716479801191</v>
       </c>
       <c r="W7" t="n">
-        <v>202.6909182596774</v>
+        <v>438.7625662397965</v>
       </c>
       <c r="X7" t="n">
-        <v>353.721709283871</v>
+        <v>504.8615974591521</v>
       </c>
       <c r="Y7" t="n">
-        <v>465.1310099629032</v>
+        <v>616.2708981381843</v>
       </c>
     </row>
     <row r="8">
@@ -4771,46 +4771,46 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>112.4501851396645</v>
+        <v>141.4463380542246</v>
       </c>
       <c r="C8" t="n">
-        <v>62.47586368209485</v>
+        <v>91.47201659665494</v>
       </c>
       <c r="D8" t="n">
-        <v>52.03227202568092</v>
+        <v>81.02842494024101</v>
       </c>
       <c r="E8" t="n">
-        <v>47.62490878641967</v>
+        <v>76.62106170097975</v>
       </c>
       <c r="F8" t="n">
-        <v>42.68588988943799</v>
+        <v>71.68204280399807</v>
       </c>
       <c r="G8" t="n">
-        <v>38.89056434699738</v>
+        <v>67.88671726155745</v>
       </c>
       <c r="H8" t="n">
-        <v>30.8</v>
+        <v>59.79615291456007</v>
       </c>
       <c r="I8" t="n">
         <v>30.8</v>
       </c>
       <c r="J8" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="K8" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="L8" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="M8" t="n">
         <v>396.55</v>
       </c>
-      <c r="K8" t="n">
+      <c r="N8" t="n">
         <v>396.55</v>
       </c>
-      <c r="L8" t="n">
-        <v>396.55</v>
-      </c>
-      <c r="M8" t="n">
+      <c r="O8" t="n">
         <v>777.6999999999999</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1158.85</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1158.85</v>
       </c>
       <c r="P8" t="n">
         <v>1158.85</v>
@@ -4822,25 +4822,25 @@
         <v>1540</v>
       </c>
       <c r="S8" t="n">
-        <v>1415.197616982083</v>
+        <v>1444.193769896644</v>
       </c>
       <c r="T8" t="n">
-        <v>1226.636423316867</v>
+        <v>1255.632576231427</v>
       </c>
       <c r="U8" t="n">
-        <v>974.8977399344323</v>
+        <v>1003.893892848992</v>
       </c>
       <c r="V8" t="n">
-        <v>742.7249882507717</v>
+        <v>771.7211411653319</v>
       </c>
       <c r="W8" t="n">
-        <v>501.9436993811278</v>
+        <v>530.9398522956878</v>
       </c>
       <c r="X8" t="n">
-        <v>307.7196251784331</v>
+        <v>336.7157780929932</v>
       </c>
       <c r="Y8" t="n">
-        <v>195.2777739836791</v>
+        <v>224.2739268982392</v>
       </c>
     </row>
     <row r="9">
@@ -4895,25 +4895,25 @@
         <v>1186.232420368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1011.404879873102</v>
+        <v>1186.232420368536</v>
       </c>
       <c r="R9" t="n">
-        <v>848.922759206675</v>
+        <v>797.3435314796468</v>
       </c>
       <c r="S9" t="n">
-        <v>460.0338703177861</v>
+        <v>730.1071678790294</v>
       </c>
       <c r="T9" t="n">
-        <v>454.6219862596914</v>
+        <v>724.6952838209346</v>
       </c>
       <c r="U9" t="n">
-        <v>454.4095016534421</v>
+        <v>335.8063949320457</v>
       </c>
       <c r="V9" t="n">
-        <v>439.752262066048</v>
+        <v>321.1491553446516</v>
       </c>
       <c r="W9" t="n">
-        <v>50.86337317715914</v>
+        <v>288.4490109912895</v>
       </c>
       <c r="X9" t="n">
         <v>30.8</v>
@@ -4929,31 +4929,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>683.9495284302473</v>
+        <v>728.2150004875771</v>
       </c>
       <c r="C10" t="n">
-        <v>809.9515342486831</v>
+        <v>854.2170063060129</v>
       </c>
       <c r="D10" t="n">
-        <v>923.2706783736832</v>
+        <v>937.2672170287502</v>
       </c>
       <c r="E10" t="n">
-        <v>1041.099582585096</v>
+        <v>1055.096121240163</v>
       </c>
       <c r="F10" t="n">
-        <v>1165.460555177032</v>
+        <v>1055.096121240163</v>
       </c>
       <c r="G10" t="n">
-        <v>1318.867121063917</v>
+        <v>1208.502687127049</v>
       </c>
       <c r="H10" t="n">
-        <v>1318.867121063917</v>
+        <v>1208.502687127049</v>
       </c>
       <c r="I10" t="n">
-        <v>1540</v>
+        <v>1429.635566063132</v>
       </c>
       <c r="J10" t="n">
-        <v>1540</v>
+        <v>1429.635566063132</v>
       </c>
       <c r="K10" t="n">
         <v>1540</v>
@@ -4986,19 +4986,19 @@
         <v>218.8756791588049</v>
       </c>
       <c r="U10" t="n">
-        <v>222.3400068538156</v>
+        <v>465.4268717970915</v>
       </c>
       <c r="V10" t="n">
-        <v>421.1613997397616</v>
+        <v>465.4268717970915</v>
       </c>
       <c r="W10" t="n">
-        <v>421.1613997397616</v>
+        <v>465.4268717970915</v>
       </c>
       <c r="X10" t="n">
-        <v>572.1921907639551</v>
+        <v>616.457662821285</v>
       </c>
       <c r="Y10" t="n">
-        <v>572.1921907639551</v>
+        <v>616.457662821285</v>
       </c>
     </row>
     <row r="11">
@@ -5038,19 +5038,19 @@
         <v>791.0663663478683</v>
       </c>
       <c r="L11" t="n">
-        <v>791.0663663478683</v>
+        <v>1698.095860917491</v>
       </c>
       <c r="M11" t="n">
-        <v>1301.915195076803</v>
+        <v>2208.944689646426</v>
       </c>
       <c r="N11" t="n">
-        <v>1915.135514851567</v>
+        <v>2822.165009421189</v>
       </c>
       <c r="O11" t="n">
-        <v>2868.178058873523</v>
+        <v>3775.207553443145</v>
       </c>
       <c r="P11" t="n">
-        <v>3729.766022780631</v>
+        <v>3775.207553443145</v>
       </c>
       <c r="Q11" t="n">
         <v>4068</v>
@@ -5108,28 +5108,28 @@
         <v>81.36</v>
       </c>
       <c r="I12" t="n">
-        <v>89.15487796756496</v>
+        <v>81.36</v>
       </c>
       <c r="J12" t="n">
-        <v>435.8613981428639</v>
+        <v>428.066520175299</v>
       </c>
       <c r="K12" t="n">
-        <v>847.8042142372474</v>
+        <v>840.0093362696824</v>
       </c>
       <c r="L12" t="n">
-        <v>1341.904675832448</v>
+        <v>1334.109797864882</v>
       </c>
       <c r="M12" t="n">
-        <v>1650.735217575307</v>
+        <v>1498.312447681983</v>
       </c>
       <c r="N12" t="n">
-        <v>2006.765502182875</v>
+        <v>1854.342732289551</v>
       </c>
       <c r="O12" t="n">
-        <v>2264.733656412845</v>
+        <v>2316.13518397327</v>
       </c>
       <c r="P12" t="n">
-        <v>2600.013000882351</v>
+        <v>2651.414528442776</v>
       </c>
       <c r="Q12" t="n">
         <v>2651.414528442776</v>
@@ -5202,19 +5202,19 @@
         <v>425.5789893823512</v>
       </c>
       <c r="N13" t="n">
-        <v>425.5789893823512</v>
+        <v>81.36</v>
       </c>
       <c r="O13" t="n">
-        <v>425.5789893823512</v>
+        <v>81.36</v>
       </c>
       <c r="P13" t="n">
-        <v>425.5789893823512</v>
+        <v>81.36</v>
       </c>
       <c r="Q13" t="n">
-        <v>425.5789893823512</v>
+        <v>81.36</v>
       </c>
       <c r="R13" t="n">
-        <v>220.1210906089449</v>
+        <v>81.36</v>
       </c>
       <c r="S13" t="n">
         <v>81.36</v>
@@ -5245,22 +5245,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1223.616245745725</v>
+        <v>1229.164925096351</v>
       </c>
       <c r="C14" t="n">
-        <v>996.8742475204788</v>
+        <v>1002.422926871105</v>
       </c>
       <c r="D14" t="n">
-        <v>809.6629790963881</v>
+        <v>815.2116584470142</v>
       </c>
       <c r="E14" t="n">
-        <v>628.48793908945</v>
+        <v>634.0366184400762</v>
       </c>
       <c r="F14" t="n">
-        <v>446.7812434247916</v>
+        <v>452.3299227754177</v>
       </c>
       <c r="G14" t="n">
-        <v>266.2182411146742</v>
+        <v>271.7669204653003</v>
       </c>
       <c r="H14" t="n">
         <v>81.36</v>
@@ -5275,13 +5275,13 @@
         <v>1182.375479385524</v>
       </c>
       <c r="L14" t="n">
-        <v>1182.375479385524</v>
+        <v>1643.743792536527</v>
       </c>
       <c r="M14" t="n">
-        <v>1693.224308114459</v>
+        <v>2154.592621265462</v>
       </c>
       <c r="N14" t="n">
-        <v>2306.444627889222</v>
+        <v>2767.812941040225</v>
       </c>
       <c r="O14" t="n">
         <v>2767.812941040225</v>
@@ -5293,28 +5293,28 @@
         <v>4068</v>
       </c>
       <c r="R14" t="n">
-        <v>4036.311321832915</v>
+        <v>4041.860001183541</v>
       </c>
       <c r="S14" t="n">
-        <v>3763.737414961882</v>
+        <v>3769.286094312508</v>
       </c>
       <c r="T14" t="n">
-        <v>3398.408544528989</v>
+        <v>3403.957223879615</v>
       </c>
       <c r="U14" t="n">
-        <v>2969.902184378877</v>
+        <v>2975.450863729503</v>
       </c>
       <c r="V14" t="n">
-        <v>2560.961755927539</v>
+        <v>2566.510435278165</v>
       </c>
       <c r="W14" t="n">
-        <v>2143.412790290219</v>
+        <v>2148.961469640845</v>
       </c>
       <c r="X14" t="n">
-        <v>1772.421039319847</v>
+        <v>1777.969718670473</v>
       </c>
       <c r="Y14" t="n">
-        <v>1483.211511357417</v>
+        <v>1488.760190708043</v>
       </c>
     </row>
     <row r="15">
@@ -5345,25 +5345,25 @@
         <v>81.36</v>
       </c>
       <c r="I15" t="n">
-        <v>89.15487796756496</v>
+        <v>81.36</v>
       </c>
       <c r="J15" t="n">
-        <v>435.8613981428639</v>
+        <v>428.066520175299</v>
       </c>
       <c r="K15" t="n">
-        <v>847.8042142372474</v>
+        <v>840.0093362696824</v>
       </c>
       <c r="L15" t="n">
-        <v>1341.904675832448</v>
+        <v>1334.109797864882</v>
       </c>
       <c r="M15" t="n">
-        <v>1650.735217575307</v>
+        <v>1642.940339607742</v>
       </c>
       <c r="N15" t="n">
-        <v>2006.765502182875</v>
+        <v>1998.97062421531</v>
       </c>
       <c r="O15" t="n">
-        <v>2468.557953866594</v>
+        <v>2264.733656412845</v>
       </c>
       <c r="P15" t="n">
         <v>2600.013000882351</v>
@@ -5403,16 +5403,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>142.1192396673154</v>
+        <v>202.8632818122532</v>
       </c>
       <c r="C16" t="n">
-        <v>142.1192396673154</v>
+        <v>202.8632818122532</v>
       </c>
       <c r="D16" t="n">
-        <v>142.1192396673154</v>
+        <v>141.7155868066416</v>
       </c>
       <c r="E16" t="n">
-        <v>85.57287114513709</v>
+        <v>85.16921828446326</v>
       </c>
       <c r="F16" t="n">
         <v>85.16921828446326</v>
@@ -5430,49 +5430,49 @@
         <v>317.0766195885342</v>
       </c>
       <c r="K16" t="n">
-        <v>317.0766195885342</v>
+        <v>252.9142218096019</v>
       </c>
       <c r="L16" t="n">
-        <v>317.0766195885342</v>
+        <v>252.9142218096019</v>
       </c>
       <c r="M16" t="n">
-        <v>317.0766195885342</v>
+        <v>252.9142218096019</v>
       </c>
       <c r="N16" t="n">
-        <v>317.0766195885342</v>
+        <v>252.9142218096019</v>
       </c>
       <c r="O16" t="n">
-        <v>317.0766195885342</v>
+        <v>89.1650171292157</v>
       </c>
       <c r="P16" t="n">
-        <v>317.0766195885342</v>
+        <v>89.1650171292157</v>
       </c>
       <c r="Q16" t="n">
-        <v>317.0766195885342</v>
+        <v>89.1650171292157</v>
       </c>
       <c r="R16" t="n">
-        <v>317.0766195885342</v>
+        <v>89.1650171292157</v>
       </c>
       <c r="S16" t="n">
-        <v>178.3155289795893</v>
+        <v>89.1650171292157</v>
       </c>
       <c r="T16" t="n">
-        <v>193.1412081383942</v>
+        <v>103.9906962880206</v>
       </c>
       <c r="U16" t="n">
-        <v>266.4424007766809</v>
+        <v>177.2918889263072</v>
       </c>
       <c r="V16" t="n">
-        <v>292.0137936626268</v>
+        <v>202.8632818122532</v>
       </c>
       <c r="W16" t="n">
-        <v>290.6271170578696</v>
+        <v>202.8632818122532</v>
       </c>
       <c r="X16" t="n">
-        <v>267.956768138569</v>
+        <v>202.8632818122532</v>
       </c>
       <c r="Y16" t="n">
-        <v>204.860452129011</v>
+        <v>202.8632818122532</v>
       </c>
     </row>
     <row r="17">
@@ -5485,19 +5485,19 @@
         <v>1229.164925096351</v>
       </c>
       <c r="C17" t="n">
-        <v>1002.422926871105</v>
+        <v>996.8742475204788</v>
       </c>
       <c r="D17" t="n">
-        <v>815.2116584470142</v>
+        <v>809.6629790963881</v>
       </c>
       <c r="E17" t="n">
-        <v>634.0366184400762</v>
+        <v>628.48793908945</v>
       </c>
       <c r="F17" t="n">
-        <v>452.3299227754177</v>
+        <v>446.7812434247916</v>
       </c>
       <c r="G17" t="n">
-        <v>271.7669204653003</v>
+        <v>266.2182411146742</v>
       </c>
       <c r="H17" t="n">
         <v>81.36</v>
@@ -5506,25 +5506,25 @@
         <v>81.36</v>
       </c>
       <c r="J17" t="n">
-        <v>472.6691130376557</v>
+        <v>396.8920737197113</v>
       </c>
       <c r="K17" t="n">
-        <v>1182.375479385524</v>
+        <v>396.8920737197113</v>
       </c>
       <c r="L17" t="n">
-        <v>2089.404973955146</v>
+        <v>1303.921568289334</v>
       </c>
       <c r="M17" t="n">
-        <v>2600.253802684082</v>
+        <v>1814.770397018269</v>
       </c>
       <c r="N17" t="n">
-        <v>3213.474122458845</v>
+        <v>1814.770397018269</v>
       </c>
       <c r="O17" t="n">
-        <v>4068</v>
+        <v>2767.812941040225</v>
       </c>
       <c r="P17" t="n">
-        <v>4068</v>
+        <v>3629.400904947332</v>
       </c>
       <c r="Q17" t="n">
         <v>4068</v>
@@ -5594,13 +5594,13 @@
         <v>1341.904675832448</v>
       </c>
       <c r="M18" t="n">
-        <v>1650.735217575307</v>
+        <v>1446.910920121557</v>
       </c>
       <c r="N18" t="n">
-        <v>2006.765502182875</v>
+        <v>1802.941204729126</v>
       </c>
       <c r="O18" t="n">
-        <v>2468.557953866594</v>
+        <v>2264.733656412845</v>
       </c>
       <c r="P18" t="n">
         <v>2600.013000882351</v>
@@ -5640,76 +5640,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>164.789588586616</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="C19" t="n">
-        <v>116.5822687401062</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="D19" t="n">
-        <v>85.16921828446326</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="E19" t="n">
-        <v>85.16921828446326</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="F19" t="n">
-        <v>85.16921828446326</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="G19" t="n">
-        <v>85.16921828446326</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="H19" t="n">
+        <v>189.862369793817</v>
+      </c>
+      <c r="I19" t="n">
+        <v>237.7452487298999</v>
+      </c>
+      <c r="J19" t="n">
+        <v>425.5789893823512</v>
+      </c>
+      <c r="K19" t="n">
+        <v>425.5789893823512</v>
+      </c>
+      <c r="L19" t="n">
+        <v>425.5789893823512</v>
+      </c>
+      <c r="M19" t="n">
+        <v>425.5789893823512</v>
+      </c>
+      <c r="N19" t="n">
+        <v>425.5789893823512</v>
+      </c>
+      <c r="O19" t="n">
         <v>81.36</v>
       </c>
-      <c r="I19" t="n">
-        <v>129.2428789360829</v>
-      </c>
-      <c r="J19" t="n">
-        <v>317.0766195885342</v>
-      </c>
-      <c r="K19" t="n">
-        <v>317.0766195885342</v>
-      </c>
-      <c r="L19" t="n">
-        <v>317.0766195885342</v>
-      </c>
-      <c r="M19" t="n">
-        <v>317.0766195885342</v>
-      </c>
-      <c r="N19" t="n">
-        <v>317.0766195885342</v>
-      </c>
-      <c r="O19" t="n">
-        <v>317.0766195885342</v>
-      </c>
       <c r="P19" t="n">
-        <v>317.0766195885342</v>
+        <v>81.36</v>
       </c>
       <c r="Q19" t="n">
-        <v>317.0766195885342</v>
+        <v>81.36</v>
       </c>
       <c r="R19" t="n">
-        <v>317.0766195885342</v>
+        <v>81.36</v>
       </c>
       <c r="S19" t="n">
-        <v>178.3155289795893</v>
+        <v>81.36</v>
       </c>
       <c r="T19" t="n">
-        <v>193.1412081383942</v>
+        <v>96.18567915880486</v>
       </c>
       <c r="U19" t="n">
-        <v>266.4424007766809</v>
+        <v>169.4868717970915</v>
       </c>
       <c r="V19" t="n">
-        <v>292.0137936626268</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="W19" t="n">
-        <v>290.6271170578696</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="X19" t="n">
-        <v>290.6271170578696</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="Y19" t="n">
-        <v>227.5308010483116</v>
+        <v>193.6715880782802</v>
       </c>
     </row>
     <row r="20">
@@ -5719,43 +5719,43 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1229.164925096351</v>
+        <v>1223.616245745725</v>
       </c>
       <c r="C20" t="n">
-        <v>1002.422926871105</v>
+        <v>996.8742475204788</v>
       </c>
       <c r="D20" t="n">
-        <v>815.2116584470142</v>
+        <v>809.6629790963881</v>
       </c>
       <c r="E20" t="n">
-        <v>634.0366184400762</v>
+        <v>628.48793908945</v>
       </c>
       <c r="F20" t="n">
-        <v>452.3299227754177</v>
+        <v>446.7812434247916</v>
       </c>
       <c r="G20" t="n">
-        <v>271.7669204653003</v>
+        <v>266.2182411146742</v>
       </c>
       <c r="H20" t="n">
-        <v>86.90867935062613</v>
+        <v>81.36</v>
       </c>
       <c r="I20" t="n">
         <v>81.36</v>
       </c>
       <c r="J20" t="n">
-        <v>472.6691130376557</v>
+        <v>81.36</v>
       </c>
       <c r="K20" t="n">
-        <v>1182.375479385524</v>
+        <v>791.0663663478683</v>
       </c>
       <c r="L20" t="n">
-        <v>2089.404973955146</v>
+        <v>1698.095860917491</v>
       </c>
       <c r="M20" t="n">
-        <v>2600.253802684082</v>
+        <v>2063.138041150613</v>
       </c>
       <c r="N20" t="n">
-        <v>3213.474122458845</v>
+        <v>2676.358360925376</v>
       </c>
       <c r="O20" t="n">
         <v>3629.400904947332</v>
@@ -5822,22 +5822,22 @@
         <v>89.15487796756496</v>
       </c>
       <c r="J21" t="n">
-        <v>435.8613981428639</v>
+        <v>232.0371006891147</v>
       </c>
       <c r="K21" t="n">
-        <v>847.8042142372474</v>
+        <v>643.9799167834981</v>
       </c>
       <c r="L21" t="n">
-        <v>1341.904675832448</v>
+        <v>1138.080378378698</v>
       </c>
       <c r="M21" t="n">
-        <v>1650.735217575307</v>
+        <v>1446.910920121557</v>
       </c>
       <c r="N21" t="n">
-        <v>2006.765502182875</v>
+        <v>1802.941204729126</v>
       </c>
       <c r="O21" t="n">
-        <v>2468.557953866594</v>
+        <v>2264.733656412845</v>
       </c>
       <c r="P21" t="n">
         <v>2600.013000882351</v>
@@ -5877,52 +5877,52 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>193.6715880782802</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="C22" t="n">
-        <v>193.6715880782802</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="D22" t="n">
-        <v>193.6715880782802</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="E22" t="n">
-        <v>193.6715880782802</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="F22" t="n">
-        <v>193.6715880782802</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="G22" t="n">
-        <v>193.6715880782802</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="H22" t="n">
-        <v>189.862369793817</v>
+        <v>191.2490463985742</v>
       </c>
       <c r="I22" t="n">
-        <v>237.7452487298999</v>
+        <v>239.1319253346571</v>
       </c>
       <c r="J22" t="n">
-        <v>425.5789893823512</v>
+        <v>426.9656659871084</v>
       </c>
       <c r="K22" t="n">
-        <v>425.5789893823512</v>
+        <v>426.9656659871084</v>
       </c>
       <c r="L22" t="n">
-        <v>425.5789893823512</v>
+        <v>426.9656659871084</v>
       </c>
       <c r="M22" t="n">
-        <v>425.5789893823512</v>
+        <v>426.9656659871084</v>
       </c>
       <c r="N22" t="n">
-        <v>425.5789893823512</v>
+        <v>426.9656659871084</v>
       </c>
       <c r="O22" t="n">
-        <v>425.5789893823512</v>
+        <v>81.36</v>
       </c>
       <c r="P22" t="n">
-        <v>425.5789893823512</v>
+        <v>81.36</v>
       </c>
       <c r="Q22" t="n">
-        <v>425.5789893823512</v>
+        <v>81.36</v>
       </c>
       <c r="R22" t="n">
         <v>81.36</v>
@@ -5940,13 +5940,13 @@
         <v>195.0582646830375</v>
       </c>
       <c r="W22" t="n">
-        <v>193.6715880782802</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="X22" t="n">
-        <v>193.6715880782802</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="Y22" t="n">
-        <v>193.6715880782802</v>
+        <v>195.0582646830375</v>
       </c>
     </row>
     <row r="23">
@@ -5956,22 +5956,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1229.164925096351</v>
+        <v>1223.616245745725</v>
       </c>
       <c r="C23" t="n">
-        <v>1002.422926871105</v>
+        <v>996.8742475204788</v>
       </c>
       <c r="D23" t="n">
-        <v>815.2116584470142</v>
+        <v>809.6629790963881</v>
       </c>
       <c r="E23" t="n">
-        <v>634.0366184400762</v>
+        <v>628.48793908945</v>
       </c>
       <c r="F23" t="n">
-        <v>452.3299227754177</v>
+        <v>446.7812434247916</v>
       </c>
       <c r="G23" t="n">
-        <v>271.7669204653003</v>
+        <v>266.2182411146742</v>
       </c>
       <c r="H23" t="n">
         <v>81.36</v>
@@ -5983,19 +5983,19 @@
         <v>472.6691130376557</v>
       </c>
       <c r="K23" t="n">
-        <v>1182.375479385524</v>
+        <v>472.6691130376557</v>
       </c>
       <c r="L23" t="n">
-        <v>2089.404973955146</v>
+        <v>690.7012485145707</v>
       </c>
       <c r="M23" t="n">
-        <v>2600.253802684082</v>
+        <v>1201.550077243506</v>
       </c>
       <c r="N23" t="n">
-        <v>3213.474122458845</v>
+        <v>1814.770397018269</v>
       </c>
       <c r="O23" t="n">
-        <v>3629.400904947332</v>
+        <v>2767.812941040225</v>
       </c>
       <c r="P23" t="n">
         <v>3629.400904947332</v>
@@ -6025,7 +6025,7 @@
         <v>1777.969718670473</v>
       </c>
       <c r="Y23" t="n">
-        <v>1488.760190708043</v>
+        <v>1483.211511357417</v>
       </c>
     </row>
     <row r="24">
@@ -6056,28 +6056,28 @@
         <v>81.36</v>
       </c>
       <c r="I24" t="n">
-        <v>89.15487796756496</v>
+        <v>81.36</v>
       </c>
       <c r="J24" t="n">
-        <v>232.0371006891147</v>
+        <v>428.066520175299</v>
       </c>
       <c r="K24" t="n">
-        <v>643.9799167834981</v>
+        <v>695.3814443439232</v>
       </c>
       <c r="L24" t="n">
-        <v>1138.080378378698</v>
+        <v>1189.481905939123</v>
       </c>
       <c r="M24" t="n">
-        <v>1446.910920121557</v>
+        <v>1498.312447681983</v>
       </c>
       <c r="N24" t="n">
-        <v>1802.941204729126</v>
+        <v>1854.342732289551</v>
       </c>
       <c r="O24" t="n">
-        <v>2264.733656412845</v>
+        <v>2316.13518397327</v>
       </c>
       <c r="P24" t="n">
-        <v>2600.013000882351</v>
+        <v>2651.414528442776</v>
       </c>
       <c r="Q24" t="n">
         <v>2651.414528442776</v>
@@ -6114,52 +6114,52 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>193.6715880782802</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="C25" t="n">
-        <v>193.6715880782802</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="D25" t="n">
-        <v>193.6715880782802</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="E25" t="n">
-        <v>193.6715880782802</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="F25" t="n">
-        <v>193.6715880782802</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="G25" t="n">
-        <v>193.6715880782802</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="H25" t="n">
-        <v>189.862369793817</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="I25" t="n">
-        <v>237.7452487298999</v>
+        <v>242.9411436191204</v>
       </c>
       <c r="J25" t="n">
-        <v>425.5789893823512</v>
+        <v>430.7748842715717</v>
       </c>
       <c r="K25" t="n">
-        <v>425.5789893823512</v>
+        <v>430.7748842715717</v>
       </c>
       <c r="L25" t="n">
-        <v>425.5789893823512</v>
+        <v>230.2217245162392</v>
       </c>
       <c r="M25" t="n">
-        <v>425.5789893823512</v>
+        <v>230.2217245162392</v>
       </c>
       <c r="N25" t="n">
-        <v>425.5789893823512</v>
+        <v>230.2217245162392</v>
       </c>
       <c r="O25" t="n">
-        <v>425.5789893823512</v>
+        <v>230.2217245162392</v>
       </c>
       <c r="P25" t="n">
-        <v>425.5789893823512</v>
+        <v>230.2217245162392</v>
       </c>
       <c r="Q25" t="n">
-        <v>425.5789893823512</v>
+        <v>230.2217245162392</v>
       </c>
       <c r="R25" t="n">
         <v>81.36</v>
@@ -6177,13 +6177,13 @@
         <v>195.0582646830375</v>
       </c>
       <c r="W25" t="n">
-        <v>193.6715880782802</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="X25" t="n">
-        <v>193.6715880782802</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="Y25" t="n">
-        <v>193.6715880782802</v>
+        <v>195.0582646830375</v>
       </c>
     </row>
     <row r="26">
@@ -6217,22 +6217,22 @@
         <v>81.36</v>
       </c>
       <c r="J26" t="n">
-        <v>472.6691130376557</v>
+        <v>81.36</v>
       </c>
       <c r="K26" t="n">
-        <v>472.6691130376557</v>
+        <v>791.0663663478683</v>
       </c>
       <c r="L26" t="n">
-        <v>1379.698607607278</v>
+        <v>1552.289212421678</v>
       </c>
       <c r="M26" t="n">
-        <v>1890.547436336213</v>
+        <v>2063.138041150613</v>
       </c>
       <c r="N26" t="n">
-        <v>2503.767756110976</v>
+        <v>2676.358360925376</v>
       </c>
       <c r="O26" t="n">
-        <v>2767.812941040225</v>
+        <v>3629.400904947332</v>
       </c>
       <c r="P26" t="n">
         <v>3629.400904947332</v>
@@ -6308,7 +6308,7 @@
         <v>1650.735217575307</v>
       </c>
       <c r="N27" t="n">
-        <v>2006.765502182875</v>
+        <v>1802.941204729126</v>
       </c>
       <c r="O27" t="n">
         <v>2264.733656412845</v>
@@ -6433,22 +6433,22 @@
         <v>1229.164925096351</v>
       </c>
       <c r="C29" t="n">
-        <v>1002.422926871105</v>
+        <v>996.8742475204788</v>
       </c>
       <c r="D29" t="n">
-        <v>815.2116584470142</v>
+        <v>809.6629790963881</v>
       </c>
       <c r="E29" t="n">
-        <v>634.0366184400762</v>
+        <v>628.48793908945</v>
       </c>
       <c r="F29" t="n">
-        <v>452.3299227754177</v>
+        <v>446.7812434247916</v>
       </c>
       <c r="G29" t="n">
-        <v>271.7669204653003</v>
+        <v>266.2182411146742</v>
       </c>
       <c r="H29" t="n">
-        <v>86.90867935062613</v>
+        <v>81.36</v>
       </c>
       <c r="I29" t="n">
         <v>81.36</v>
@@ -6457,19 +6457,19 @@
         <v>472.6691130376557</v>
       </c>
       <c r="K29" t="n">
-        <v>1182.375479385524</v>
+        <v>645.2597178520556</v>
       </c>
       <c r="L29" t="n">
-        <v>1643.743792536527</v>
+        <v>1552.289212421678</v>
       </c>
       <c r="M29" t="n">
-        <v>2154.592621265462</v>
+        <v>2063.138041150613</v>
       </c>
       <c r="N29" t="n">
-        <v>2767.812941040225</v>
+        <v>2676.358360925376</v>
       </c>
       <c r="O29" t="n">
-        <v>2767.812941040225</v>
+        <v>3629.400904947332</v>
       </c>
       <c r="P29" t="n">
         <v>3629.400904947332</v>
@@ -6542,16 +6542,16 @@
         <v>1341.904675832448</v>
       </c>
       <c r="M30" t="n">
-        <v>1446.910920121557</v>
+        <v>1650.735217575307</v>
       </c>
       <c r="N30" t="n">
-        <v>1802.941204729126</v>
+        <v>1854.342732289551</v>
       </c>
       <c r="O30" t="n">
-        <v>2264.733656412845</v>
+        <v>2316.13518397327</v>
       </c>
       <c r="P30" t="n">
-        <v>2600.013000882351</v>
+        <v>2651.414528442776</v>
       </c>
       <c r="Q30" t="n">
         <v>2651.414528442776</v>
@@ -6588,55 +6588,55 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>193.6715880782802</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="C31" t="n">
-        <v>193.6715880782802</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="D31" t="n">
-        <v>193.6715880782802</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="E31" t="n">
-        <v>193.6715880782802</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="F31" t="n">
-        <v>193.6715880782802</v>
+        <v>148.070387991434</v>
       </c>
       <c r="G31" t="n">
-        <v>193.6715880782802</v>
+        <v>148.070387991434</v>
       </c>
       <c r="H31" t="n">
-        <v>189.862369793817</v>
+        <v>144.2611697069707</v>
       </c>
       <c r="I31" t="n">
-        <v>237.7452487298999</v>
+        <v>192.1440486430537</v>
       </c>
       <c r="J31" t="n">
-        <v>425.5789893823512</v>
+        <v>379.977789295505</v>
       </c>
       <c r="K31" t="n">
-        <v>425.5789893823512</v>
+        <v>379.977789295505</v>
       </c>
       <c r="L31" t="n">
-        <v>425.5789893823512</v>
+        <v>379.977789295505</v>
       </c>
       <c r="M31" t="n">
-        <v>425.5789893823512</v>
+        <v>81.36</v>
       </c>
       <c r="N31" t="n">
-        <v>425.5789893823512</v>
+        <v>81.36</v>
       </c>
       <c r="O31" t="n">
-        <v>425.5789893823512</v>
+        <v>81.36</v>
       </c>
       <c r="P31" t="n">
-        <v>425.5789893823512</v>
+        <v>81.36</v>
       </c>
       <c r="Q31" t="n">
-        <v>425.5789893823512</v>
+        <v>81.36</v>
       </c>
       <c r="R31" t="n">
-        <v>220.1210906089449</v>
+        <v>81.36</v>
       </c>
       <c r="S31" t="n">
         <v>81.36</v>
@@ -6651,13 +6651,13 @@
         <v>195.0582646830375</v>
       </c>
       <c r="W31" t="n">
-        <v>193.6715880782802</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="X31" t="n">
-        <v>193.6715880782802</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="Y31" t="n">
-        <v>193.6715880782802</v>
+        <v>195.0582646830375</v>
       </c>
     </row>
     <row r="32">
@@ -6694,37 +6694,37 @@
         <v>472.6691130376557</v>
       </c>
       <c r="K32" t="n">
-        <v>472.6691130376557</v>
+        <v>1182.375479385524</v>
       </c>
       <c r="L32" t="n">
-        <v>1379.698607607278</v>
+        <v>2089.404973955146</v>
       </c>
       <c r="M32" t="n">
-        <v>1890.547436336213</v>
+        <v>2600.253802684082</v>
       </c>
       <c r="N32" t="n">
-        <v>2253.369492070936</v>
+        <v>3213.474122458845</v>
       </c>
       <c r="O32" t="n">
-        <v>3206.412036092893</v>
+        <v>3213.474122458845</v>
       </c>
       <c r="P32" t="n">
-        <v>4068</v>
+        <v>3629.400904947332</v>
       </c>
       <c r="Q32" t="n">
         <v>4068</v>
       </c>
       <c r="R32" t="n">
-        <v>4041.860001183541</v>
+        <v>4036.311321832915</v>
       </c>
       <c r="S32" t="n">
-        <v>3769.286094312508</v>
+        <v>3763.737414961882</v>
       </c>
       <c r="T32" t="n">
-        <v>3403.957223879615</v>
+        <v>3398.408544528989</v>
       </c>
       <c r="U32" t="n">
-        <v>2975.450863729503</v>
+        <v>2969.902184378877</v>
       </c>
       <c r="V32" t="n">
         <v>2560.961755927539</v>
@@ -6767,28 +6767,28 @@
         <v>81.36</v>
       </c>
       <c r="I33" t="n">
-        <v>89.15487796756496</v>
+        <v>81.36</v>
       </c>
       <c r="J33" t="n">
-        <v>435.8613981428639</v>
+        <v>428.066520175299</v>
       </c>
       <c r="K33" t="n">
-        <v>847.8042142372474</v>
+        <v>840.0093362696824</v>
       </c>
       <c r="L33" t="n">
-        <v>1341.904675832448</v>
+        <v>1334.109797864882</v>
       </c>
       <c r="M33" t="n">
-        <v>1650.735217575307</v>
+        <v>1642.940339607742</v>
       </c>
       <c r="N33" t="n">
-        <v>2006.765502182875</v>
+        <v>1998.97062421531</v>
       </c>
       <c r="O33" t="n">
-        <v>2468.557953866594</v>
+        <v>2460.763075899029</v>
       </c>
       <c r="P33" t="n">
-        <v>2600.013000882351</v>
+        <v>2651.414528442776</v>
       </c>
       <c r="Q33" t="n">
         <v>2651.414528442776</v>
@@ -6825,55 +6825,55 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>193.6715880782802</v>
+        <v>172.3879157637369</v>
       </c>
       <c r="C34" t="n">
-        <v>193.6715880782802</v>
+        <v>172.3879157637369</v>
       </c>
       <c r="D34" t="n">
-        <v>193.6715880782802</v>
+        <v>172.3879157637369</v>
       </c>
       <c r="E34" t="n">
-        <v>193.6715880782802</v>
+        <v>172.3879157637369</v>
       </c>
       <c r="F34" t="n">
-        <v>193.6715880782802</v>
+        <v>172.3879157637369</v>
       </c>
       <c r="G34" t="n">
-        <v>193.6715880782802</v>
+        <v>172.3879157637369</v>
       </c>
       <c r="H34" t="n">
-        <v>189.862369793817</v>
+        <v>168.5786974792737</v>
       </c>
       <c r="I34" t="n">
-        <v>237.7452487298999</v>
+        <v>216.4615764153566</v>
       </c>
       <c r="J34" t="n">
-        <v>425.5789893823512</v>
+        <v>404.2953170678079</v>
       </c>
       <c r="K34" t="n">
-        <v>425.5789893823512</v>
+        <v>404.2953170678079</v>
       </c>
       <c r="L34" t="n">
-        <v>425.5789893823512</v>
+        <v>404.2953170678079</v>
       </c>
       <c r="M34" t="n">
-        <v>425.5789893823512</v>
+        <v>404.2953170678079</v>
       </c>
       <c r="N34" t="n">
-        <v>425.5789893823512</v>
+        <v>404.2953170678079</v>
       </c>
       <c r="O34" t="n">
-        <v>425.5789893823512</v>
+        <v>81.36</v>
       </c>
       <c r="P34" t="n">
-        <v>220.1210906089449</v>
+        <v>81.36</v>
       </c>
       <c r="Q34" t="n">
-        <v>220.1210906089449</v>
+        <v>81.36</v>
       </c>
       <c r="R34" t="n">
-        <v>220.1210906089449</v>
+        <v>81.36</v>
       </c>
       <c r="S34" t="n">
         <v>81.36</v>
@@ -6888,13 +6888,13 @@
         <v>195.0582646830375</v>
       </c>
       <c r="W34" t="n">
-        <v>193.6715880782802</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="X34" t="n">
-        <v>193.6715880782802</v>
+        <v>172.3879157637369</v>
       </c>
       <c r="Y34" t="n">
-        <v>193.6715880782802</v>
+        <v>172.3879157637369</v>
       </c>
     </row>
     <row r="35">
@@ -6904,76 +6904,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C35" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D35" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E35" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F35" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G35" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H35" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I35" t="n">
         <v>44.72</v>
       </c>
       <c r="J35" t="n">
-        <v>64.92117127106515</v>
+        <v>44.72</v>
       </c>
       <c r="K35" t="n">
-        <v>618.3311712710652</v>
+        <v>598.13</v>
       </c>
       <c r="L35" t="n">
-        <v>1171.741171271065</v>
+        <v>1151.54</v>
       </c>
       <c r="M35" t="n">
-        <v>1682.59</v>
+        <v>1151.54</v>
       </c>
       <c r="N35" t="n">
-        <v>1682.59</v>
+        <v>1151.54</v>
       </c>
       <c r="O35" t="n">
-        <v>1682.59</v>
+        <v>1704.95</v>
       </c>
       <c r="P35" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q35" t="n">
         <v>2236</v>
       </c>
       <c r="R35" t="n">
-        <v>2236</v>
+        <v>2231.994554156147</v>
       </c>
       <c r="S35" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T35" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U35" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V35" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W35" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X35" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y35" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="36">
@@ -6983,25 +6983,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>472.7782575464261</v>
+        <v>391.4553531635761</v>
       </c>
       <c r="C36" t="n">
-        <v>461.5662247731743</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="D36" t="n">
-        <v>461.5662247731743</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="E36" t="n">
-        <v>461.5662247731743</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="F36" t="n">
-        <v>461.5662247731743</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="G36" t="n">
-        <v>461.5662247731743</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="H36" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="I36" t="n">
         <v>44.72</v>
@@ -7049,10 +7049,10 @@
         <v>628.142589726071</v>
       </c>
       <c r="X36" t="n">
-        <v>557.5741660438614</v>
+        <v>476.2512616610114</v>
       </c>
       <c r="Y36" t="n">
-        <v>507.6838703204934</v>
+        <v>426.3609659376434</v>
       </c>
     </row>
     <row r="37">
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>870.0458296400257</v>
+        <v>877.7566123122328</v>
       </c>
       <c r="C37" t="n">
-        <v>946.5478354584615</v>
+        <v>954.2586181306687</v>
       </c>
       <c r="D37" t="n">
         <v>1010.366979583462</v>
@@ -7116,22 +7116,22 @@
         <v>44.72</v>
       </c>
       <c r="T37" t="n">
-        <v>175.5848964865977</v>
+        <v>183.2956791588049</v>
       </c>
       <c r="U37" t="n">
-        <v>372.6360891248843</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V37" t="n">
-        <v>521.9574820108303</v>
+        <v>529.6682646830375</v>
       </c>
       <c r="W37" t="n">
-        <v>644.3484002705077</v>
+        <v>652.0591829427149</v>
       </c>
       <c r="X37" t="n">
-        <v>745.8791912947012</v>
+        <v>753.5899739669084</v>
       </c>
       <c r="Y37" t="n">
-        <v>807.7884919737335</v>
+        <v>815.4992746459407</v>
       </c>
     </row>
     <row r="38">
@@ -7141,22 +7141,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C38" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D38" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E38" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F38" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G38" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H38" t="n">
         <v>44.72</v>
@@ -7165,52 +7165,52 @@
         <v>44.72</v>
       </c>
       <c r="J38" t="n">
-        <v>179.7320762183976</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K38" t="n">
-        <v>733.1420762183976</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L38" t="n">
-        <v>733.1420762183976</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="M38" t="n">
-        <v>1243.990904947333</v>
+        <v>575.7700000000003</v>
       </c>
       <c r="N38" t="n">
-        <v>1243.990904947333</v>
+        <v>1129.18</v>
       </c>
       <c r="O38" t="n">
-        <v>1797.400904947332</v>
+        <v>1682.59</v>
       </c>
       <c r="P38" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q38" t="n">
         <v>2236</v>
       </c>
       <c r="R38" t="n">
-        <v>2236</v>
+        <v>2231.994554156147</v>
       </c>
       <c r="S38" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T38" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U38" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V38" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W38" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X38" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y38" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="39">
@@ -7220,22 +7220,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>119.2429040110725</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C39" t="n">
-        <v>108.0308712378207</v>
+        <v>44.72</v>
       </c>
       <c r="D39" t="n">
-        <v>108.0308712378207</v>
+        <v>44.72</v>
       </c>
       <c r="E39" t="n">
-        <v>108.0308712378207</v>
+        <v>44.72</v>
       </c>
       <c r="F39" t="n">
-        <v>108.0308712378207</v>
+        <v>44.72</v>
       </c>
       <c r="G39" t="n">
-        <v>108.0308712378207</v>
+        <v>44.72</v>
       </c>
       <c r="H39" t="n">
         <v>44.72</v>
@@ -7274,22 +7274,22 @@
         <v>883.1445443513733</v>
       </c>
       <c r="T39" t="n">
-        <v>827.2276097882281</v>
+        <v>763.9167385504073</v>
       </c>
       <c r="U39" t="n">
-        <v>776.5100746769283</v>
+        <v>713.1992034391076</v>
       </c>
       <c r="V39" t="n">
-        <v>711.3477845844836</v>
+        <v>648.036913346663</v>
       </c>
       <c r="W39" t="n">
-        <v>628.142589726071</v>
+        <v>211.2963649528968</v>
       </c>
       <c r="X39" t="n">
-        <v>557.5741660438614</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y39" t="n">
-        <v>154.1485167851398</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="40">
@@ -7359,7 +7359,7 @@
         <v>380.3468717970915</v>
       </c>
       <c r="V40" t="n">
-        <v>521.9574820108303</v>
+        <v>529.6682646830375</v>
       </c>
       <c r="W40" t="n">
         <v>644.3484002705077</v>
@@ -7378,46 +7378,46 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C41" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D41" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E41" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F41" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G41" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H41" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I41" t="n">
         <v>44.72</v>
       </c>
       <c r="J41" t="n">
-        <v>64.92117127106526</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K41" t="n">
-        <v>618.3311712710653</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L41" t="n">
-        <v>618.3311712710653</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="M41" t="n">
-        <v>1129.18</v>
+        <v>946.8779417665908</v>
       </c>
       <c r="N41" t="n">
-        <v>1682.59</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="O41" t="n">
-        <v>1682.59</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="P41" t="n">
         <v>2236</v>
@@ -7426,28 +7426,28 @@
         <v>2236</v>
       </c>
       <c r="R41" t="n">
-        <v>2236</v>
+        <v>2231.994554156147</v>
       </c>
       <c r="S41" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T41" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U41" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V41" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W41" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X41" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y41" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="42">
@@ -7457,10 +7457,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>407.3842417608302</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C42" t="n">
-        <v>396.1722089875784</v>
+        <v>44.72</v>
       </c>
       <c r="D42" t="n">
         <v>44.72</v>
@@ -7505,28 +7505,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R42" t="n">
-        <v>935.4919426714454</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S42" t="n">
-        <v>817.7505285657774</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T42" t="n">
-        <v>761.8335940026321</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U42" t="n">
-        <v>711.1160588913324</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V42" t="n">
-        <v>645.9537687988877</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W42" t="n">
-        <v>562.7485739404751</v>
+        <v>564.8317184882503</v>
       </c>
       <c r="X42" t="n">
-        <v>492.1801502582655</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y42" t="n">
-        <v>442.2898545348975</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="43">
@@ -7590,16 +7590,16 @@
         <v>44.72</v>
       </c>
       <c r="T43" t="n">
-        <v>175.5848964865977</v>
+        <v>183.2956791588049</v>
       </c>
       <c r="U43" t="n">
-        <v>372.6360891248843</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V43" t="n">
-        <v>521.9574820108303</v>
+        <v>529.6682646830375</v>
       </c>
       <c r="W43" t="n">
-        <v>644.3484002705077</v>
+        <v>652.0591829427149</v>
       </c>
       <c r="X43" t="n">
         <v>745.8791912947012</v>
@@ -7615,22 +7615,22 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C44" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D44" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E44" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F44" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G44" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H44" t="n">
         <v>44.72</v>
@@ -7639,25 +7639,25 @@
         <v>44.72</v>
       </c>
       <c r="J44" t="n">
-        <v>44.72</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K44" t="n">
-        <v>44.72</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L44" t="n">
-        <v>179.7320762183977</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="M44" t="n">
-        <v>690.5809049473327</v>
+        <v>946.8779417665908</v>
       </c>
       <c r="N44" t="n">
-        <v>1243.990904947333</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="O44" t="n">
-        <v>1797.400904947332</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="P44" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q44" t="n">
         <v>2236</v>
@@ -7669,22 +7669,22 @@
         <v>2089.688719391593</v>
       </c>
       <c r="T44" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U44" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V44" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W44" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X44" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y44" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="45">
@@ -7694,7 +7694,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>119.2429040110725</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C45" t="n">
         <v>44.72</v>
@@ -7742,28 +7742,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R45" t="n">
-        <v>647.3506049216877</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S45" t="n">
-        <v>529.6091908160197</v>
+        <v>819.8336731135525</v>
       </c>
       <c r="T45" t="n">
-        <v>473.6922562528744</v>
+        <v>763.9167385504073</v>
       </c>
       <c r="U45" t="n">
-        <v>422.9747211415747</v>
+        <v>713.1992034391076</v>
       </c>
       <c r="V45" t="n">
-        <v>357.8124310491301</v>
+        <v>294.5015598113094</v>
       </c>
       <c r="W45" t="n">
-        <v>274.6072361907174</v>
+        <v>211.2963649528968</v>
       </c>
       <c r="X45" t="n">
-        <v>204.0388125085078</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y45" t="n">
-        <v>154.1485167851397</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="46">
@@ -7964,7 +7964,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>35.04300624509033</v>
+        <v>404.4874506895348</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -7982,7 +7982,7 @@
         <v>455.2478695740924</v>
       </c>
       <c r="P2" t="n">
-        <v>369.7315044851259</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q2" t="n">
         <v>172.8226843274854</v>
@@ -8201,22 +8201,22 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>420.0430062450903</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="L5" t="n">
-        <v>369.4444444444444</v>
+        <v>369.4444444444445</v>
       </c>
       <c r="M5" t="n">
-        <v>544.2621276423173</v>
+        <v>929.2621276423173</v>
       </c>
       <c r="N5" t="n">
         <v>862.2489580698352</v>
       </c>
       <c r="O5" t="n">
-        <v>455.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P5" t="n">
         <v>0.2870600406814136</v>
@@ -8438,7 +8438,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>404.4874506895348</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -8447,16 +8447,16 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>929.2621276423173</v>
+        <v>913.7065720867618</v>
       </c>
       <c r="N8" t="n">
-        <v>862.2489580698352</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O8" t="n">
-        <v>70.24786957409245</v>
+        <v>455.2478695740924</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2870600406814136</v>
+        <v>385.2870600406814</v>
       </c>
       <c r="Q8" t="n">
         <v>557.8226843274854</v>
@@ -8681,7 +8681,7 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>916.1914086561842</v>
       </c>
       <c r="M11" t="n">
         <v>1060.271045550332</v>
@@ -8693,10 +8693,10 @@
         <v>1032.917105959907</v>
       </c>
       <c r="P11" t="n">
-        <v>870.5779326741233</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q11" t="n">
-        <v>514.4731663672521</v>
+        <v>468.5726303445106</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8918,7 +8918,7 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>466.0285991424271</v>
       </c>
       <c r="M14" t="n">
         <v>1060.271045550332</v>
@@ -8927,7 +8927,7 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O14" t="n">
-        <v>536.2764687165196</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P14" t="n">
         <v>870.5779326741233</v>
@@ -9149,10 +9149,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>430.3047365861567</v>
+        <v>353.7622726286371</v>
       </c>
       <c r="K17" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>916.1914086561842</v>
@@ -9161,16 +9161,16 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N17" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O17" t="n">
-        <v>933.4053216358654</v>
+        <v>1032.917105959907</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2870600406814136</v>
+        <v>870.5779326741233</v>
       </c>
       <c r="Q17" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9386,7 +9386,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K20" t="n">
         <v>716.8751175230994</v>
@@ -9395,13 +9395,13 @@
         <v>916.1914086561842</v>
       </c>
       <c r="M20" t="n">
-        <v>1060.271045550332</v>
+        <v>912.9916026252691</v>
       </c>
       <c r="N20" t="n">
         <v>1096.663422488788</v>
       </c>
       <c r="O20" t="n">
-        <v>490.3759326937771</v>
+        <v>1032.917105959907</v>
       </c>
       <c r="P20" t="n">
         <v>0.2870600406814136</v>
@@ -9626,10 +9626,10 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K23" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>916.1914086561842</v>
+        <v>220.2344802797121</v>
       </c>
       <c r="M23" t="n">
         <v>1060.271045550332</v>
@@ -9638,10 +9638,10 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O23" t="n">
-        <v>490.3759326937771</v>
+        <v>1032.917105959907</v>
       </c>
       <c r="P23" t="n">
-        <v>0.2870600406814136</v>
+        <v>870.5779326741233</v>
       </c>
       <c r="Q23" t="n">
         <v>615.8520732695737</v>
@@ -9860,13 +9860,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J26" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L26" t="n">
-        <v>916.1914086561842</v>
+        <v>768.9119657311207</v>
       </c>
       <c r="M26" t="n">
         <v>1060.271045550332</v>
@@ -9875,10 +9875,10 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O26" t="n">
-        <v>336.9601775834349</v>
+        <v>1032.917105959907</v>
       </c>
       <c r="P26" t="n">
-        <v>870.5779326741233</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q26" t="n">
         <v>615.8520732695737</v>
@@ -10100,10 +10100,10 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K29" t="n">
-        <v>716.8751175230994</v>
+        <v>174.3339442569695</v>
       </c>
       <c r="L29" t="n">
-        <v>466.0285991424271</v>
+        <v>916.1914086561842</v>
       </c>
       <c r="M29" t="n">
         <v>1060.271045550332</v>
@@ -10112,10 +10112,10 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O29" t="n">
-        <v>70.24786957409245</v>
+        <v>1032.917105959907</v>
       </c>
       <c r="P29" t="n">
-        <v>870.5779326741233</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q29" t="n">
         <v>615.8520732695737</v>
@@ -10337,7 +10337,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L32" t="n">
         <v>916.1914086561842</v>
@@ -10346,16 +10346,16 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N32" t="n">
-        <v>843.735883054404</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O32" t="n">
-        <v>1032.917105959907</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P32" t="n">
-        <v>870.5779326741233</v>
+        <v>420.4151231603661</v>
       </c>
       <c r="Q32" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10571,28 +10571,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J35" t="n">
-        <v>55.44822975121676</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K35" t="n">
         <v>559</v>
       </c>
       <c r="L35" t="n">
-        <v>559</v>
+        <v>559.0000000000001</v>
       </c>
       <c r="M35" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N35" t="n">
         <v>477.2489580698352</v>
       </c>
       <c r="O35" t="n">
-        <v>70.24786957409245</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P35" t="n">
-        <v>559.2870600406815</v>
+        <v>93.67181251273416</v>
       </c>
       <c r="Q35" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10808,28 +10808,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J38" t="n">
-        <v>171.4188408091283</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K38" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>1060.271045550332</v>
+        <v>685.4145387153926</v>
       </c>
       <c r="N38" t="n">
-        <v>477.2489580698352</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O38" t="n">
         <v>629.2478695740924</v>
       </c>
       <c r="P38" t="n">
-        <v>0.2870600406814136</v>
+        <v>559.2870600406815</v>
       </c>
       <c r="Q38" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -11045,10 +11045,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>55.44822975121687</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K41" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -11060,10 +11060,10 @@
         <v>1036.248958069835</v>
       </c>
       <c r="O41" t="n">
-        <v>70.24786957409245</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P41" t="n">
-        <v>559.2870600406815</v>
+        <v>184.4305532057413</v>
       </c>
       <c r="Q41" t="n">
         <v>172.8226843274854</v>
@@ -11282,13 +11282,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>136.375834564038</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
         <v>1060.271045550332</v>
@@ -11300,10 +11300,10 @@
         <v>629.2478695740924</v>
       </c>
       <c r="P44" t="n">
-        <v>0.2870600406814136</v>
+        <v>184.4305532057413</v>
       </c>
       <c r="Q44" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -22700,7 +22700,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.591170646055957</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -22712,7 +22712,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.591170646055843</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -23417,7 +23417,7 @@
         <v>295.6316114025499</v>
       </c>
       <c r="N13" t="n">
-        <v>346.1850752716849</v>
+        <v>5.408275783157251</v>
       </c>
       <c r="O13" t="n">
         <v>415.445564079015</v>
@@ -23429,10 +23429,10 @@
         <v>500.839266425598</v>
       </c>
       <c r="R13" t="n">
-        <v>298.1988081954788</v>
+        <v>501.6021279811511</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>137.3734797028554</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -23618,19 +23618,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>62.11380033707866</v>
       </c>
       <c r="C16" t="n">
         <v>47.72524664804467</v>
       </c>
       <c r="D16" t="n">
-        <v>60.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>48.98323963567484</v>
+        <v>49.38285596774193</v>
       </c>
       <c r="G16" t="n">
         <v>20.04387284153003</v>
@@ -23645,7 +23645,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>63.52077380114304</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>198.5476281577792</v>
@@ -23657,7 +23657,7 @@
         <v>346.1850752716849</v>
       </c>
       <c r="O16" t="n">
-        <v>415.445564079015</v>
+        <v>253.3338514454326</v>
       </c>
       <c r="P16" t="n">
         <v>462.4478973282775</v>
@@ -23669,7 +23669,7 @@
         <v>501.6021279811511</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>137.3734797028554</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -23681,13 +23681,13 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.372809838709685</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>22.44364543010755</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>62.46535284946236</v>
       </c>
     </row>
     <row r="17">
@@ -23855,13 +23855,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>62.11380033707866</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>47.72524664804467</v>
       </c>
       <c r="D19" t="n">
-        <v>29.43729810446895</v>
+        <v>60.53621805555548</v>
       </c>
       <c r="E19" t="n">
         <v>55.98090483695654</v>
@@ -23894,7 +23894,7 @@
         <v>346.1850752716849</v>
       </c>
       <c r="O19" t="n">
-        <v>415.445564079015</v>
+        <v>74.66876459048729</v>
       </c>
       <c r="P19" t="n">
         <v>462.4478973282775</v>
@@ -23906,7 +23906,7 @@
         <v>501.6021279811511</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>137.3734797028554</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -23924,7 +23924,7 @@
         <v>22.44364543010755</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>62.46535284946236</v>
       </c>
     </row>
     <row r="20">
@@ -24131,7 +24131,7 @@
         <v>346.1850752716849</v>
       </c>
       <c r="O22" t="n">
-        <v>415.445564079015</v>
+        <v>73.29595475177763</v>
       </c>
       <c r="P22" t="n">
         <v>462.4478973282775</v>
@@ -24140,7 +24140,7 @@
         <v>500.839266425598</v>
       </c>
       <c r="R22" t="n">
-        <v>160.8253284926234</v>
+        <v>501.6021279811511</v>
       </c>
       <c r="S22" t="n">
         <v>137.3734797028554</v>
@@ -24155,7 +24155,7 @@
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.372809838709685</v>
       </c>
       <c r="X22" t="n">
         <v>22.44364543010755</v>
@@ -24347,7 +24347,7 @@
         <v>20.04387284153003</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>3.77112610161862</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -24359,7 +24359,7 @@
         <v>63.52077380114304</v>
       </c>
       <c r="L25" t="n">
-        <v>198.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
         <v>295.6316114025499</v>
@@ -24377,7 +24377,7 @@
         <v>500.839266425598</v>
       </c>
       <c r="R25" t="n">
-        <v>160.8253284926234</v>
+        <v>354.2290207100743</v>
       </c>
       <c r="S25" t="n">
         <v>137.3734797028554</v>
@@ -24392,7 +24392,7 @@
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.372809838709685</v>
       </c>
       <c r="X25" t="n">
         <v>22.44364543010755</v>
@@ -24815,7 +24815,7 @@
         <v>55.98090483695654</v>
       </c>
       <c r="F31" t="n">
-        <v>49.38285596774193</v>
+        <v>2.86485804305449</v>
       </c>
       <c r="G31" t="n">
         <v>20.04387284153003</v>
@@ -24836,7 +24836,7 @@
         <v>198.5476281577792</v>
       </c>
       <c r="M31" t="n">
-        <v>295.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
         <v>346.1850752716849</v>
@@ -24851,10 +24851,10 @@
         <v>500.839266425598</v>
       </c>
       <c r="R31" t="n">
-        <v>298.1988081954788</v>
+        <v>501.6021279811511</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>137.3734797028554</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -24866,7 +24866,7 @@
         <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.372809838709685</v>
       </c>
       <c r="X31" t="n">
         <v>22.44364543010755</v>
@@ -25079,10 +25079,10 @@
         <v>346.1850752716849</v>
       </c>
       <c r="O34" t="n">
-        <v>415.445564079015</v>
+        <v>95.73960018188518</v>
       </c>
       <c r="P34" t="n">
-        <v>259.0445775426052</v>
+        <v>462.4478973282775</v>
       </c>
       <c r="Q34" t="n">
         <v>500.839266425598</v>
@@ -25091,7 +25091,7 @@
         <v>501.6021279811511</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>137.3734797028554</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -25103,10 +25103,10 @@
         <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.372809838709685</v>
       </c>
       <c r="X34" t="n">
-        <v>22.44364543010755</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
         <v>62.46535284946236</v>
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6326538.530966838</v>
+        <v>6326538.530966835</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7336594.241408327</v>
+        <v>7336594.241408325</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8346649.951849815</v>
+        <v>8346649.951849814</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9356705.662291305</v>
+        <v>9356705.662291303</v>
       </c>
     </row>
     <row r="11">
@@ -26278,19 +26278,19 @@
         <v>1133404.96701338</v>
       </c>
       <c r="E2" t="n">
-        <v>1069470.752232171</v>
+        <v>1069470.75223217</v>
       </c>
       <c r="F2" t="n">
         <v>1069470.75223217</v>
       </c>
       <c r="G2" t="n">
-        <v>1069470.75223217</v>
+        <v>1069470.752232171</v>
       </c>
       <c r="H2" t="n">
         <v>1069470.75223217</v>
       </c>
       <c r="I2" t="n">
-        <v>1069470.752232169</v>
+        <v>1069470.75223217</v>
       </c>
       <c r="J2" t="n">
         <v>1069470.752232171</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>570914.1248995091</v>
+        <v>572429.9805878249</v>
       </c>
       <c r="C4" t="n">
-        <v>568856.1447656949</v>
+        <v>570372.0004540107</v>
       </c>
       <c r="D4" t="n">
-        <v>566795.372853379</v>
+        <v>568311.2285416948</v>
       </c>
       <c r="E4" t="n">
-        <v>445852.6895118617</v>
+        <v>448189.3974235593</v>
       </c>
       <c r="F4" t="n">
-        <v>444399.1387482318</v>
+        <v>446735.8466599294</v>
       </c>
       <c r="G4" t="n">
-        <v>442943.5821390834</v>
+        <v>445280.2900507811</v>
       </c>
       <c r="H4" t="n">
-        <v>441486.0053004215</v>
+        <v>443822.7132121192</v>
       </c>
       <c r="I4" t="n">
-        <v>440026.3936608351</v>
+        <v>442363.1015725328</v>
       </c>
       <c r="J4" t="n">
-        <v>438564.7324579426</v>
+        <v>440901.4403696402</v>
       </c>
       <c r="K4" t="n">
-        <v>437101.0067347542</v>
+        <v>439437.7146464519</v>
       </c>
       <c r="L4" t="n">
-        <v>435635.201335937</v>
+        <v>437971.9092476346</v>
       </c>
       <c r="M4" t="n">
-        <v>527474.7245421007</v>
+        <v>529216.5743552083</v>
       </c>
       <c r="N4" t="n">
-        <v>525509.8275072473</v>
+        <v>527251.677320355</v>
       </c>
       <c r="O4" t="n">
-        <v>523542.0882495091</v>
+        <v>525283.9380626167</v>
       </c>
       <c r="P4" t="n">
-        <v>521571.4853984989</v>
+        <v>523313.3352116066</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>369935.2421138712</v>
+        <v>368419.3864255551</v>
       </c>
       <c r="C6" t="n">
-        <v>507513.2222476854</v>
+        <v>505997.3665593694</v>
       </c>
       <c r="D6" t="n">
-        <v>509573.994160001</v>
+        <v>508058.1384716852</v>
       </c>
       <c r="E6" t="n">
-        <v>140404.937720309</v>
+        <v>138068.2298086109</v>
       </c>
       <c r="F6" t="n">
-        <v>544322.4884839386</v>
+        <v>541985.7805722411</v>
       </c>
       <c r="G6" t="n">
-        <v>545778.045093087</v>
+        <v>543441.3371813896</v>
       </c>
       <c r="H6" t="n">
-        <v>547235.6219317489</v>
+        <v>544898.914020051</v>
       </c>
       <c r="I6" t="n">
-        <v>548695.2335713344</v>
+        <v>546358.5256596374</v>
       </c>
       <c r="J6" t="n">
-        <v>234636.8947742281</v>
+        <v>232300.1868625307</v>
       </c>
       <c r="K6" t="n">
-        <v>551620.6204974162</v>
+        <v>549283.9125857186</v>
       </c>
       <c r="L6" t="n">
-        <v>553086.4258962329</v>
+        <v>550749.7179845353</v>
       </c>
       <c r="M6" t="n">
-        <v>381305.2617572347</v>
+        <v>379563.4119441268</v>
       </c>
       <c r="N6" t="n">
-        <v>544518.1587920876</v>
+        <v>542776.3089789802</v>
       </c>
       <c r="O6" t="n">
-        <v>366485.8980498263</v>
+        <v>364744.0482367184</v>
       </c>
       <c r="P6" t="n">
-        <v>548456.5009008362</v>
+        <v>546714.6510877286</v>
       </c>
     </row>
   </sheetData>
@@ -26987,19 +26987,19 @@
         <v>-0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H2" t="n">
         <v>-0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>225</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>-0</v>
@@ -27030,13 +27030,13 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -27481,10 +27481,10 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>250.8785988282945</v>
+        <v>222.1724074428797</v>
       </c>
       <c r="S2" t="n">
-        <v>371.2938086145853</v>
+        <v>400</v>
       </c>
       <c r="T2" t="n">
         <v>400</v>
@@ -27518,7 +27518,7 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D3" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>342.6720972219126</v>
@@ -27527,7 +27527,7 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
-        <v>325.7395358750273</v>
+        <v>206.1572493711352</v>
       </c>
       <c r="H3" t="n">
         <v>332.1680871864211</v>
@@ -27560,10 +27560,10 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>162.2737972923793</v>
+        <v>400</v>
       </c>
       <c r="S3" t="n">
-        <v>170.2062293060259</v>
+        <v>400</v>
       </c>
       <c r="T3" t="n">
         <v>400</v>
@@ -27591,7 +27591,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>287.1138003370787</v>
+        <v>287.8802402048284</v>
       </c>
       <c r="C4" t="n">
         <v>272.7252466480447</v>
@@ -27603,19 +27603,19 @@
         <v>400</v>
       </c>
       <c r="F4" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G4" t="n">
-        <v>245.04387284153</v>
+        <v>400</v>
       </c>
       <c r="H4" t="n">
-        <v>228.7711261016186</v>
+        <v>400</v>
       </c>
       <c r="I4" t="n">
-        <v>378.5330718402562</v>
+        <v>400</v>
       </c>
       <c r="J4" t="n">
-        <v>400</v>
+        <v>35.26894883590776</v>
       </c>
       <c r="K4" t="n">
         <v>400</v>
@@ -27648,19 +27648,19 @@
         <v>210.0245665062577</v>
       </c>
       <c r="U4" t="n">
+        <v>150.9583912744579</v>
+      </c>
+      <c r="V4" t="n">
         <v>400</v>
       </c>
-      <c r="V4" t="n">
-        <v>199.1703102162162</v>
-      </c>
       <c r="W4" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X4" t="n">
         <v>400</v>
       </c>
       <c r="Y4" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="5">
@@ -27749,7 +27749,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>84.9101973533833</v>
+        <v>382.2185369131728</v>
       </c>
       <c r="C6" t="n">
         <v>361.0999124455193</v>
@@ -27758,10 +27758,10 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>325.7395358750273</v>
@@ -27818,7 +27818,7 @@
         <v>400</v>
       </c>
       <c r="Y6" t="n">
-        <v>14.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="7">
@@ -27828,10 +27828,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>400</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C7" t="n">
-        <v>400</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D7" t="n">
         <v>400</v>
@@ -27840,22 +27840,22 @@
         <v>400</v>
       </c>
       <c r="F7" t="n">
+        <v>274.3828559677419</v>
+      </c>
+      <c r="G7" t="n">
+        <v>245.04387284153</v>
+      </c>
+      <c r="H7" t="n">
+        <v>228.7711261016186</v>
+      </c>
+      <c r="I7" t="n">
         <v>400</v>
       </c>
-      <c r="G7" t="n">
+      <c r="J7" t="n">
         <v>400</v>
       </c>
-      <c r="H7" t="n">
+      <c r="K7" t="n">
         <v>400</v>
-      </c>
-      <c r="I7" t="n">
-        <v>336.9137329713681</v>
-      </c>
-      <c r="J7" t="n">
-        <v>35.26894883590776</v>
-      </c>
-      <c r="K7" t="n">
-        <v>288.520773801143</v>
       </c>
       <c r="L7" t="n">
         <v>400</v>
@@ -27879,7 +27879,7 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
-        <v>362.3734797028554</v>
+        <v>400</v>
       </c>
       <c r="T7" t="n">
         <v>210.0245665062577</v>
@@ -27888,13 +27888,13 @@
         <v>150.9583912744579</v>
       </c>
       <c r="V7" t="n">
-        <v>199.1703102162162</v>
+        <v>400</v>
       </c>
       <c r="W7" t="n">
         <v>400</v>
       </c>
       <c r="X7" t="n">
-        <v>400</v>
+        <v>314.2103436314769</v>
       </c>
       <c r="Y7" t="n">
         <v>400</v>
@@ -27928,7 +27928,7 @@
         <v>400</v>
       </c>
       <c r="I8" t="n">
-        <v>150.0811596826846</v>
+        <v>121.3749682972702</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27958,7 +27958,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S8" t="n">
-        <v>371.2938086145853</v>
+        <v>400</v>
       </c>
       <c r="T8" t="n">
         <v>400</v>
@@ -28031,28 +28031,28 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R9" t="n">
-        <v>386.4164978326168</v>
+        <v>162.2737972923793</v>
       </c>
       <c r="S9" t="n">
-        <v>81.5639999646113</v>
+        <v>400</v>
       </c>
       <c r="T9" t="n">
         <v>400</v>
       </c>
       <c r="U9" t="n">
-        <v>400</v>
+        <v>15.21035976018675</v>
       </c>
       <c r="V9" t="n">
         <v>400</v>
       </c>
       <c r="W9" t="n">
-        <v>47.37314290982852</v>
+        <v>400</v>
       </c>
       <c r="X9" t="n">
-        <v>400</v>
+        <v>164.790218564011</v>
       </c>
       <c r="Y9" t="n">
         <v>399.3913927661343</v>
@@ -28071,13 +28071,13 @@
         <v>400</v>
       </c>
       <c r="D10" t="n">
-        <v>400</v>
+        <v>369.4253197956942</v>
       </c>
       <c r="E10" t="n">
         <v>400</v>
       </c>
       <c r="F10" t="n">
-        <v>400</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G10" t="n">
         <v>400</v>
@@ -28092,7 +28092,7 @@
         <v>35.26894883590776</v>
       </c>
       <c r="K10" t="n">
-        <v>288.520773801143</v>
+        <v>400</v>
       </c>
       <c r="L10" t="n">
         <v>400</v>
@@ -28122,10 +28122,10 @@
         <v>400</v>
       </c>
       <c r="U10" t="n">
-        <v>154.4577121785092</v>
+        <v>400</v>
       </c>
       <c r="V10" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W10" t="n">
         <v>226.3728098387097</v>
@@ -28244,7 +28244,7 @@
         <v>225</v>
       </c>
       <c r="I12" t="n">
-        <v>225</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J12" t="n">
         <v>225</v>
@@ -28256,19 +28256,19 @@
         <v>225</v>
       </c>
       <c r="M12" t="n">
-        <v>225</v>
+        <v>78.91122027701098</v>
       </c>
       <c r="N12" t="n">
         <v>225</v>
       </c>
       <c r="O12" t="n">
-        <v>19.11687125883898</v>
+        <v>225</v>
       </c>
       <c r="P12" t="n">
         <v>225</v>
       </c>
       <c r="Q12" t="n">
-        <v>225</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R12" t="n">
         <v>225</v>
@@ -28399,7 +28399,7 @@
         <v>225</v>
       </c>
       <c r="H14" t="n">
-        <v>225</v>
+        <v>219.5068074428801</v>
       </c>
       <c r="I14" t="n">
         <v>150.0811596826846</v>
@@ -28429,7 +28429,7 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>219.5068074428802</v>
+        <v>225</v>
       </c>
       <c r="S14" t="n">
         <v>225</v>
@@ -28481,7 +28481,7 @@
         <v>225</v>
       </c>
       <c r="I15" t="n">
-        <v>225</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J15" t="n">
         <v>225</v>
@@ -28499,10 +28499,10 @@
         <v>225</v>
       </c>
       <c r="O15" t="n">
-        <v>225</v>
+        <v>26.99048536749061</v>
       </c>
       <c r="P15" t="n">
-        <v>19.11687125883908</v>
+        <v>225</v>
       </c>
       <c r="Q15" t="n">
         <v>225</v>
@@ -28621,7 +28621,7 @@
         <v>225</v>
       </c>
       <c r="C17" t="n">
-        <v>225</v>
+        <v>219.5068074428802</v>
       </c>
       <c r="D17" t="n">
         <v>225</v>
@@ -28636,7 +28636,7 @@
         <v>225</v>
       </c>
       <c r="H17" t="n">
-        <v>219.5068074428801</v>
+        <v>225</v>
       </c>
       <c r="I17" t="n">
         <v>150.0811596826846</v>
@@ -28730,7 +28730,7 @@
         <v>225</v>
       </c>
       <c r="M18" t="n">
-        <v>225</v>
+        <v>19.11687125883903</v>
       </c>
       <c r="N18" t="n">
         <v>225</v>
@@ -28739,7 +28739,7 @@
         <v>225</v>
       </c>
       <c r="P18" t="n">
-        <v>19.11687125883908</v>
+        <v>225</v>
       </c>
       <c r="Q18" t="n">
         <v>225</v>
@@ -28855,7 +28855,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>225</v>
+        <v>219.5068074428801</v>
       </c>
       <c r="C20" t="n">
         <v>225</v>
@@ -28876,7 +28876,7 @@
         <v>225</v>
       </c>
       <c r="I20" t="n">
-        <v>144.5879671255647</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -28958,7 +28958,7 @@
         <v>225</v>
       </c>
       <c r="J21" t="n">
-        <v>225</v>
+        <v>19.11687125883914</v>
       </c>
       <c r="K21" t="n">
         <v>225</v>
@@ -28976,7 +28976,7 @@
         <v>225</v>
       </c>
       <c r="P21" t="n">
-        <v>19.11687125883908</v>
+        <v>225</v>
       </c>
       <c r="Q21" t="n">
         <v>225</v>
@@ -29110,7 +29110,7 @@
         <v>225</v>
       </c>
       <c r="H23" t="n">
-        <v>219.5068074428801</v>
+        <v>225</v>
       </c>
       <c r="I23" t="n">
         <v>150.0811596826846</v>
@@ -29161,7 +29161,7 @@
         <v>225</v>
       </c>
       <c r="Y23" t="n">
-        <v>225</v>
+        <v>219.5068074428801</v>
       </c>
     </row>
     <row r="24">
@@ -29192,13 +29192,13 @@
         <v>225</v>
       </c>
       <c r="I24" t="n">
-        <v>225</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J24" t="n">
-        <v>19.11687125883914</v>
+        <v>225</v>
       </c>
       <c r="K24" t="n">
-        <v>225</v>
+        <v>78.91122027701095</v>
       </c>
       <c r="L24" t="n">
         <v>225</v>
@@ -29216,7 +29216,7 @@
         <v>225</v>
       </c>
       <c r="Q24" t="n">
-        <v>225</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R24" t="n">
         <v>225</v>
@@ -29444,10 +29444,10 @@
         <v>225</v>
       </c>
       <c r="N27" t="n">
-        <v>225</v>
+        <v>19.11687125883913</v>
       </c>
       <c r="O27" t="n">
-        <v>19.11687125883898</v>
+        <v>225</v>
       </c>
       <c r="P27" t="n">
         <v>225</v>
@@ -29569,7 +29569,7 @@
         <v>225</v>
       </c>
       <c r="C29" t="n">
-        <v>225</v>
+        <v>219.5068074428802</v>
       </c>
       <c r="D29" t="n">
         <v>225</v>
@@ -29587,7 +29587,7 @@
         <v>225</v>
       </c>
       <c r="I29" t="n">
-        <v>144.5879671255647</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -29678,10 +29678,10 @@
         <v>225</v>
       </c>
       <c r="M30" t="n">
-        <v>19.11687125883903</v>
+        <v>225</v>
       </c>
       <c r="N30" t="n">
-        <v>225</v>
+        <v>71.0376061683595</v>
       </c>
       <c r="O30" t="n">
         <v>225</v>
@@ -29690,7 +29690,7 @@
         <v>225</v>
       </c>
       <c r="Q30" t="n">
-        <v>225</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R30" t="n">
         <v>225</v>
@@ -29851,7 +29851,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>225</v>
+        <v>219.5068074428802</v>
       </c>
       <c r="S32" t="n">
         <v>225</v>
@@ -29863,7 +29863,7 @@
         <v>225</v>
       </c>
       <c r="V32" t="n">
-        <v>219.5068074428799</v>
+        <v>225</v>
       </c>
       <c r="W32" t="n">
         <v>225</v>
@@ -29903,7 +29903,7 @@
         <v>225</v>
       </c>
       <c r="I33" t="n">
-        <v>225</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J33" t="n">
         <v>225</v>
@@ -29924,10 +29924,10 @@
         <v>225</v>
       </c>
       <c r="P33" t="n">
-        <v>19.11687125883908</v>
+        <v>78.91122027701083</v>
       </c>
       <c r="Q33" t="n">
-        <v>225</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R33" t="n">
         <v>225</v>
@@ -30061,7 +30061,7 @@
         <v>350</v>
       </c>
       <c r="I35" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -30088,7 +30088,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>250.8785988282945</v>
+        <v>246.9132074428799</v>
       </c>
       <c r="S35" t="n">
         <v>350</v>
@@ -30137,10 +30137,10 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H36" t="n">
-        <v>136.6167105523271</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -30185,7 +30185,7 @@
         <v>350</v>
       </c>
       <c r="X36" t="n">
-        <v>350</v>
+        <v>269.4903246609786</v>
       </c>
       <c r="Y36" t="n">
         <v>350</v>
@@ -30204,7 +30204,7 @@
         <v>350</v>
       </c>
       <c r="D37" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="E37" t="n">
         <v>350</v>
@@ -30252,7 +30252,7 @@
         <v>350</v>
       </c>
       <c r="T37" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="U37" t="n">
         <v>350</v>
@@ -30295,7 +30295,7 @@
         <v>350</v>
       </c>
       <c r="H38" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="I38" t="n">
         <v>150.0811596826846</v>
@@ -30325,7 +30325,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>250.8785988282945</v>
+        <v>246.9132074428799</v>
       </c>
       <c r="S38" t="n">
         <v>350</v>
@@ -30374,7 +30374,7 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H39" t="n">
-        <v>269.4903246609787</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I39" t="n">
         <v>217.1263858913485</v>
@@ -30410,7 +30410,7 @@
         <v>350</v>
       </c>
       <c r="T39" t="n">
-        <v>350</v>
+        <v>287.3222374745575</v>
       </c>
       <c r="U39" t="n">
         <v>350</v>
@@ -30419,13 +30419,13 @@
         <v>350</v>
       </c>
       <c r="W39" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
         <v>350</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
     </row>
     <row r="40">
@@ -30495,10 +30495,10 @@
         <v>350</v>
       </c>
       <c r="V40" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="W40" t="n">
-        <v>350</v>
+        <v>342.2113306341341</v>
       </c>
       <c r="X40" t="n">
         <v>350</v>
@@ -30535,7 +30535,7 @@
         <v>350</v>
       </c>
       <c r="I41" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -30562,7 +30562,7 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>250.8785988282945</v>
+        <v>246.9132074428799</v>
       </c>
       <c r="S41" t="n">
         <v>350</v>
@@ -30599,7 +30599,7 @@
         <v>350</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E42" t="n">
         <v>342.6720972219126</v>
@@ -30641,7 +30641,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R42" t="n">
-        <v>285.25992437226</v>
+        <v>350</v>
       </c>
       <c r="S42" t="n">
         <v>350</v>
@@ -30656,10 +30656,10 @@
         <v>350</v>
       </c>
       <c r="W42" t="n">
-        <v>350</v>
+        <v>287.3222374745575</v>
       </c>
       <c r="X42" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
         <v>350</v>
@@ -30726,7 +30726,7 @@
         <v>350</v>
       </c>
       <c r="T43" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="U43" t="n">
         <v>350</v>
@@ -30738,7 +30738,7 @@
         <v>350</v>
       </c>
       <c r="X43" t="n">
-        <v>350</v>
+        <v>342.2113306341341</v>
       </c>
       <c r="Y43" t="n">
         <v>350</v>
@@ -30769,7 +30769,7 @@
         <v>350</v>
       </c>
       <c r="H44" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="I44" t="n">
         <v>150.0811596826846</v>
@@ -30805,7 +30805,7 @@
         <v>350</v>
       </c>
       <c r="T44" t="n">
-        <v>346.0346086145854</v>
+        <v>350</v>
       </c>
       <c r="U44" t="n">
         <v>350</v>
@@ -30833,7 +30833,7 @@
         <v>350</v>
       </c>
       <c r="C45" t="n">
-        <v>287.3222374745576</v>
+        <v>350</v>
       </c>
       <c r="D45" t="n">
         <v>347.9376868977026</v>
@@ -30878,10 +30878,10 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="S45" t="n">
-        <v>350</v>
+        <v>287.3222374745575</v>
       </c>
       <c r="T45" t="n">
         <v>350</v>
@@ -30890,7 +30890,7 @@
         <v>350</v>
       </c>
       <c r="V45" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
         <v>350</v>
@@ -34743,7 +34743,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>369.4444444444445</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -34761,7 +34761,7 @@
         <v>385</v>
       </c>
       <c r="P2" t="n">
-        <v>369.4444444444445</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -34877,7 +34877,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>0.7664398677497452</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -34889,19 +34889,19 @@
         <v>119.0190951630435</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>154.95612715847</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>171.2288738983814</v>
       </c>
       <c r="I4" t="n">
-        <v>201.8996162201379</v>
+        <v>223.3665443798817</v>
       </c>
       <c r="J4" t="n">
-        <v>364.7310511640923</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
         <v>111.479226198857</v>
@@ -34934,19 +34934,19 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>249.0416087255421</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W4" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>152.5563545698924</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="5">
@@ -34980,22 +34980,22 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
         <v>385</v>
       </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
       <c r="L5" t="n">
-        <v>369.4444444444444</v>
+        <v>369.4444444444445</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="N5" t="n">
         <v>385</v>
       </c>
       <c r="O5" t="n">
-        <v>385</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -35114,10 +35114,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>114.4637819444445</v>
@@ -35126,22 +35126,22 @@
         <v>119.0190951630435</v>
       </c>
       <c r="F7" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>154.95612715847</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>171.2288738983814</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>160.2802773512498</v>
+        <v>223.3665443798817</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>364.7310511640923</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>111.479226198857</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -35165,7 +35165,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>37.62652029714457</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -35174,13 +35174,13 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W7" t="n">
         <v>173.6271901612903</v>
       </c>
       <c r="X7" t="n">
-        <v>152.5563545698924</v>
+        <v>66.76669820136929</v>
       </c>
       <c r="Y7" t="n">
         <v>112.5346471505376</v>
@@ -35217,7 +35217,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>369.4444444444445</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -35226,16 +35226,16 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
+        <v>369.4444444444444</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
         <v>385</v>
       </c>
-      <c r="N8" t="n">
+      <c r="P8" t="n">
         <v>385</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>385</v>
@@ -35357,13 +35357,13 @@
         <v>127.2747533519553</v>
       </c>
       <c r="D10" t="n">
-        <v>114.4637819444445</v>
+        <v>83.88910174013874</v>
       </c>
       <c r="E10" t="n">
         <v>119.0190951630435</v>
       </c>
       <c r="F10" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
         <v>154.95612715847</v>
@@ -35378,7 +35378,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>111.479226198857</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -35408,10 +35408,10 @@
         <v>189.9754334937423</v>
       </c>
       <c r="U10" t="n">
-        <v>3.499320904051265</v>
+        <v>249.0416087255421</v>
       </c>
       <c r="V10" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
@@ -35460,7 +35460,7 @@
         <v>716.8751175230993</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>916.1914086561842</v>
       </c>
       <c r="M11" t="n">
         <v>516.0089179080152</v>
@@ -35472,10 +35472,10 @@
         <v>962.6692363858147</v>
       </c>
       <c r="P11" t="n">
-        <v>870.2908726334418</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>341.6504820397668</v>
+        <v>295.7499460170251</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35530,7 +35530,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>7.873614108651466</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>350.2086062376757</v>
@@ -35542,19 +35542,19 @@
         <v>499.091375348687</v>
       </c>
       <c r="M12" t="n">
-        <v>311.9500421645043</v>
+        <v>165.8612624415153</v>
       </c>
       <c r="N12" t="n">
         <v>359.6265501086548</v>
       </c>
       <c r="O12" t="n">
-        <v>260.5738931615854</v>
+        <v>466.4570219027464</v>
       </c>
       <c r="P12" t="n">
         <v>338.6660045146532</v>
       </c>
       <c r="Q12" t="n">
-        <v>51.92073490952041</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -35697,7 +35697,7 @@
         <v>716.8751175230996</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>466.0285991424271</v>
       </c>
       <c r="M14" t="n">
         <v>516.0089179080152</v>
@@ -35706,7 +35706,7 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O14" t="n">
-        <v>466.0285991424272</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
         <v>870.2908726334418</v>
@@ -35767,7 +35767,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>7.873614108651466</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>350.2086062376757</v>
@@ -35785,10 +35785,10 @@
         <v>359.6265501086548</v>
       </c>
       <c r="O15" t="n">
-        <v>466.4570219027464</v>
+        <v>268.4475072702369</v>
       </c>
       <c r="P15" t="n">
-        <v>132.7828757734923</v>
+        <v>338.6660045146532</v>
       </c>
       <c r="Q15" t="n">
         <v>51.92073490952041</v>
@@ -35928,10 +35928,10 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>395.2617303410664</v>
+        <v>318.7192663835467</v>
       </c>
       <c r="K17" t="n">
-        <v>716.8751175230996</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>916.1914086561842</v>
@@ -35940,16 +35940,16 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N17" t="n">
-        <v>619.4144644189528</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>863.157452061773</v>
+        <v>962.6692363858147</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>870.2908726334418</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36016,7 +36016,7 @@
         <v>499.091375348687</v>
       </c>
       <c r="M18" t="n">
-        <v>311.9500421645043</v>
+        <v>106.0669134233433</v>
       </c>
       <c r="N18" t="n">
         <v>359.6265501086548</v>
@@ -36025,7 +36025,7 @@
         <v>466.4570219027464</v>
       </c>
       <c r="P18" t="n">
-        <v>132.7828757734923</v>
+        <v>338.6660045146532</v>
       </c>
       <c r="Q18" t="n">
         <v>51.92073490952041</v>
@@ -36165,22 +36165,22 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>716.8751175230996</v>
+        <v>716.8751175230993</v>
       </c>
       <c r="L20" t="n">
         <v>916.1914086561842</v>
       </c>
       <c r="M20" t="n">
-        <v>516.0089179080152</v>
+        <v>368.7294749829518</v>
       </c>
       <c r="N20" t="n">
         <v>619.4144644189528</v>
       </c>
       <c r="O20" t="n">
-        <v>420.1280631196846</v>
+        <v>962.6692363858147</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -36244,7 +36244,7 @@
         <v>7.873614108651466</v>
       </c>
       <c r="J21" t="n">
-        <v>350.2086062376757</v>
+        <v>144.3254774965148</v>
       </c>
       <c r="K21" t="n">
         <v>416.1038546407913</v>
@@ -36262,7 +36262,7 @@
         <v>466.4570219027464</v>
       </c>
       <c r="P21" t="n">
-        <v>132.7828757734923</v>
+        <v>338.6660045146532</v>
       </c>
       <c r="Q21" t="n">
         <v>51.92073490952041</v>
@@ -36405,10 +36405,10 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K23" t="n">
-        <v>716.8751175230996</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>916.1914086561842</v>
+        <v>220.2344802797121</v>
       </c>
       <c r="M23" t="n">
         <v>516.0089179080152</v>
@@ -36417,10 +36417,10 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O23" t="n">
-        <v>420.1280631196846</v>
+        <v>962.6692363858147</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>870.2908726334418</v>
       </c>
       <c r="Q23" t="n">
         <v>443.0293889420883</v>
@@ -36478,13 +36478,13 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>7.873614108651466</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>144.3254774965148</v>
+        <v>350.2086062376757</v>
       </c>
       <c r="K24" t="n">
-        <v>416.1038546407913</v>
+        <v>270.0150749178023</v>
       </c>
       <c r="L24" t="n">
         <v>499.091375348687</v>
@@ -36502,7 +36502,7 @@
         <v>338.6660045146532</v>
       </c>
       <c r="Q24" t="n">
-        <v>51.92073490952041</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -36639,13 +36639,13 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>716.8751175230993</v>
       </c>
       <c r="L26" t="n">
-        <v>916.1914086561842</v>
+        <v>768.9119657311207</v>
       </c>
       <c r="M26" t="n">
         <v>516.0089179080152</v>
@@ -36654,10 +36654,10 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O26" t="n">
-        <v>266.7123080093424</v>
+        <v>962.6692363858147</v>
       </c>
       <c r="P26" t="n">
-        <v>870.2908726334418</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>443.0293889420883</v>
@@ -36730,10 +36730,10 @@
         <v>311.9500421645043</v>
       </c>
       <c r="N27" t="n">
-        <v>359.6265501086548</v>
+        <v>153.743421367494</v>
       </c>
       <c r="O27" t="n">
-        <v>260.5738931615854</v>
+        <v>466.4570219027464</v>
       </c>
       <c r="P27" t="n">
         <v>338.6660045146532</v>
@@ -36879,10 +36879,10 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K29" t="n">
-        <v>716.8751175230996</v>
+        <v>174.3339442569695</v>
       </c>
       <c r="L29" t="n">
-        <v>466.0285991424271</v>
+        <v>916.1914086561842</v>
       </c>
       <c r="M29" t="n">
         <v>516.0089179080152</v>
@@ -36891,10 +36891,10 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>962.6692363858147</v>
       </c>
       <c r="P29" t="n">
-        <v>870.2908726334418</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>443.0293889420883</v>
@@ -36964,10 +36964,10 @@
         <v>499.091375348687</v>
       </c>
       <c r="M30" t="n">
-        <v>106.0669134233433</v>
+        <v>311.9500421645043</v>
       </c>
       <c r="N30" t="n">
-        <v>359.6265501086548</v>
+        <v>205.6641562770143</v>
       </c>
       <c r="O30" t="n">
         <v>466.4570219027464</v>
@@ -36976,7 +36976,7 @@
         <v>338.6660045146532</v>
       </c>
       <c r="Q30" t="n">
-        <v>51.92073490952041</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -37116,7 +37116,7 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>716.8751175230996</v>
       </c>
       <c r="L32" t="n">
         <v>916.1914086561842</v>
@@ -37125,16 +37125,16 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N32" t="n">
-        <v>366.4869249845688</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O32" t="n">
-        <v>962.6692363858147</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>870.2908726334418</v>
+        <v>420.1280631196846</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37189,7 +37189,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>7.873614108651466</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
         <v>350.2086062376757</v>
@@ -37210,10 +37210,10 @@
         <v>466.4570219027464</v>
       </c>
       <c r="P33" t="n">
-        <v>132.7828757734923</v>
+        <v>192.577224791664</v>
       </c>
       <c r="Q33" t="n">
-        <v>51.92073490952041</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -37350,28 +37350,28 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>20.40522350612643</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
         <v>559</v>
       </c>
       <c r="L35" t="n">
+        <v>559.0000000000001</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
         <v>559</v>
       </c>
-      <c r="M35" t="n">
-        <v>516.0089179080152</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
       <c r="P35" t="n">
-        <v>559</v>
+        <v>93.38475247205275</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37490,7 +37490,7 @@
         <v>77.27475335195533</v>
       </c>
       <c r="D37" t="n">
-        <v>64.46378194444452</v>
+        <v>56.67511257857869</v>
       </c>
       <c r="E37" t="n">
         <v>69.01909516304346</v>
@@ -37538,7 +37538,7 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U37" t="n">
         <v>199.0416087255421</v>
@@ -37587,28 +37587,28 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>136.375834564038</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>141.1524110730753</v>
+      </c>
+      <c r="N38" t="n">
         <v>559</v>
-      </c>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" t="n">
-        <v>516.0089179080152</v>
-      </c>
-      <c r="N38" t="n">
-        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>559</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="Q38" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37781,10 +37781,10 @@
         <v>199.0416087255421</v>
       </c>
       <c r="V40" t="n">
-        <v>143.041020417918</v>
+        <v>150.8296897837838</v>
       </c>
       <c r="W40" t="n">
-        <v>123.6271901612903</v>
+        <v>115.8385207954244</v>
       </c>
       <c r="X40" t="n">
         <v>102.5563545698924</v>
@@ -37824,10 +37824,10 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>20.40522350612654</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K41" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -37839,10 +37839,10 @@
         <v>559</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="P41" t="n">
-        <v>559</v>
+        <v>184.1434931650599</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -38012,7 +38012,7 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U43" t="n">
         <v>199.0416087255421</v>
@@ -38024,7 +38024,7 @@
         <v>123.6271901612903</v>
       </c>
       <c r="X43" t="n">
-        <v>102.5563545698924</v>
+        <v>94.76768520402656</v>
       </c>
       <c r="Y43" t="n">
         <v>62.53464715053764</v>
@@ -38061,13 +38061,13 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>136.375834564038</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
         <v>516.0089179080152</v>
@@ -38079,10 +38079,10 @@
         <v>559</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>184.1434931650599</v>
       </c>
       <c r="Q44" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
